--- a/public/data/latest/master_total_vehicle_sales.xlsx
+++ b/public/data/latest/master_total_vehicle_sales.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1904"/>
+  <dimension ref="A1:C1907"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18568,20 +18568,20 @@
         <v>46235</v>
       </c>
       <c r="C1395" t="n">
-        <v>57900</v>
+        <v>57760</v>
       </c>
     </row>
     <row r="1396">
       <c r="A1396" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B1396" s="2" t="n">
-        <v>42370</v>
+        <v>46266</v>
       </c>
       <c r="C1396" t="n">
-        <v>76334</v>
+        <v>61650</v>
       </c>
     </row>
     <row r="1397">
@@ -18591,10 +18591,10 @@
         </is>
       </c>
       <c r="B1397" s="2" t="n">
-        <v>42401</v>
+        <v>42370</v>
       </c>
       <c r="C1397" t="n">
-        <v>97649</v>
+        <v>76334</v>
       </c>
     </row>
     <row r="1398">
@@ -18604,10 +18604,10 @@
         </is>
       </c>
       <c r="B1398" s="2" t="n">
-        <v>42430</v>
+        <v>42401</v>
       </c>
       <c r="C1398" t="n">
-        <v>111511</v>
+        <v>97649</v>
       </c>
     </row>
     <row r="1399">
@@ -18617,10 +18617,10 @@
         </is>
       </c>
       <c r="B1399" s="2" t="n">
-        <v>42461</v>
+        <v>42430</v>
       </c>
       <c r="C1399" t="n">
-        <v>100279</v>
+        <v>111511</v>
       </c>
     </row>
     <row r="1400">
@@ -18630,10 +18630,10 @@
         </is>
       </c>
       <c r="B1400" s="2" t="n">
-        <v>42491</v>
+        <v>42461</v>
       </c>
       <c r="C1400" t="n">
-        <v>113671</v>
+        <v>100279</v>
       </c>
     </row>
     <row r="1401">
@@ -18643,10 +18643,10 @@
         </is>
       </c>
       <c r="B1401" s="2" t="n">
-        <v>42522</v>
+        <v>42491</v>
       </c>
       <c r="C1401" t="n">
-        <v>123790</v>
+        <v>113671</v>
       </c>
     </row>
     <row r="1402">
@@ -18656,10 +18656,10 @@
         </is>
       </c>
       <c r="B1402" s="2" t="n">
-        <v>42552</v>
+        <v>42522</v>
       </c>
       <c r="C1402" t="n">
-        <v>107306</v>
+        <v>123790</v>
       </c>
     </row>
     <row r="1403">
@@ -18669,10 +18669,10 @@
         </is>
       </c>
       <c r="B1403" s="2" t="n">
-        <v>42583</v>
+        <v>42552</v>
       </c>
       <c r="C1403" t="n">
-        <v>64089</v>
+        <v>107306</v>
       </c>
     </row>
     <row r="1404">
@@ -18682,10 +18682,10 @@
         </is>
       </c>
       <c r="B1404" s="2" t="n">
-        <v>42614</v>
+        <v>42583</v>
       </c>
       <c r="C1404" t="n">
-        <v>79591</v>
+        <v>64089</v>
       </c>
     </row>
     <row r="1405">
@@ -18695,10 +18695,10 @@
         </is>
       </c>
       <c r="B1405" s="2" t="n">
-        <v>42644</v>
+        <v>42614</v>
       </c>
       <c r="C1405" t="n">
-        <v>83248</v>
+        <v>79591</v>
       </c>
     </row>
     <row r="1406">
@@ -18708,10 +18708,10 @@
         </is>
       </c>
       <c r="B1406" s="2" t="n">
-        <v>42675</v>
+        <v>42644</v>
       </c>
       <c r="C1406" t="n">
-        <v>92653</v>
+        <v>83248</v>
       </c>
     </row>
     <row r="1407">
@@ -18721,10 +18721,10 @@
         </is>
       </c>
       <c r="B1407" s="2" t="n">
-        <v>42705</v>
+        <v>42675</v>
       </c>
       <c r="C1407" t="n">
-        <v>96888</v>
+        <v>92653</v>
       </c>
     </row>
     <row r="1408">
@@ -18734,10 +18734,10 @@
         </is>
       </c>
       <c r="B1408" s="2" t="n">
-        <v>42736</v>
+        <v>42705</v>
       </c>
       <c r="C1408" t="n">
-        <v>84515</v>
+        <v>96888</v>
       </c>
     </row>
     <row r="1409">
@@ -18747,10 +18747,10 @@
         </is>
       </c>
       <c r="B1409" s="2" t="n">
-        <v>42767</v>
+        <v>42736</v>
       </c>
       <c r="C1409" t="n">
-        <v>97796</v>
+        <v>84515</v>
       </c>
     </row>
     <row r="1410">
@@ -18760,10 +18760,10 @@
         </is>
       </c>
       <c r="B1410" s="2" t="n">
-        <v>42795</v>
+        <v>42767</v>
       </c>
       <c r="C1410" t="n">
-        <v>125600</v>
+        <v>97796</v>
       </c>
     </row>
     <row r="1411">
@@ -18773,10 +18773,10 @@
         </is>
       </c>
       <c r="B1411" s="2" t="n">
-        <v>42826</v>
+        <v>42795</v>
       </c>
       <c r="C1411" t="n">
-        <v>101375</v>
+        <v>125600</v>
       </c>
     </row>
     <row r="1412">
@@ -18786,10 +18786,10 @@
         </is>
       </c>
       <c r="B1412" s="2" t="n">
-        <v>42856</v>
+        <v>42826</v>
       </c>
       <c r="C1412" t="n">
-        <v>126411</v>
+        <v>101375</v>
       </c>
     </row>
     <row r="1413">
@@ -18799,10 +18799,10 @@
         </is>
       </c>
       <c r="B1413" s="2" t="n">
-        <v>42887</v>
+        <v>42856</v>
       </c>
       <c r="C1413" t="n">
-        <v>131797</v>
+        <v>126411</v>
       </c>
     </row>
     <row r="1414">
@@ -18812,10 +18812,10 @@
         </is>
       </c>
       <c r="B1414" s="2" t="n">
-        <v>42917</v>
+        <v>42887</v>
       </c>
       <c r="C1414" t="n">
-        <v>109947</v>
+        <v>131797</v>
       </c>
     </row>
     <row r="1415">
@@ -18825,10 +18825,10 @@
         </is>
       </c>
       <c r="B1415" s="2" t="n">
-        <v>42948</v>
+        <v>42917</v>
       </c>
       <c r="C1415" t="n">
-        <v>72410</v>
+        <v>109947</v>
       </c>
     </row>
     <row r="1416">
@@ -18838,10 +18838,10 @@
         </is>
       </c>
       <c r="B1416" s="2" t="n">
-        <v>42979</v>
+        <v>42948</v>
       </c>
       <c r="C1416" t="n">
-        <v>83291</v>
+        <v>72410</v>
       </c>
     </row>
     <row r="1417">
@@ -18851,10 +18851,10 @@
         </is>
       </c>
       <c r="B1417" s="2" t="n">
-        <v>43009</v>
+        <v>42979</v>
       </c>
       <c r="C1417" t="n">
-        <v>94676</v>
+        <v>83291</v>
       </c>
     </row>
     <row r="1418">
@@ -18864,10 +18864,10 @@
         </is>
       </c>
       <c r="B1418" s="2" t="n">
-        <v>43040</v>
+        <v>43009</v>
       </c>
       <c r="C1418" t="n">
-        <v>104170</v>
+        <v>94676</v>
       </c>
     </row>
     <row r="1419">
@@ -18877,10 +18877,10 @@
         </is>
       </c>
       <c r="B1419" s="2" t="n">
-        <v>43070</v>
+        <v>43040</v>
       </c>
       <c r="C1419" t="n">
-        <v>102944</v>
+        <v>104170</v>
       </c>
     </row>
     <row r="1420">
@@ -18890,10 +18890,10 @@
         </is>
       </c>
       <c r="B1420" s="2" t="n">
-        <v>43101</v>
+        <v>43070</v>
       </c>
       <c r="C1420" t="n">
-        <v>101661</v>
+        <v>102944</v>
       </c>
     </row>
     <row r="1421">
@@ -18903,10 +18903,10 @@
         </is>
       </c>
       <c r="B1421" s="2" t="n">
-        <v>43132</v>
+        <v>43101</v>
       </c>
       <c r="C1421" t="n">
-        <v>110475</v>
+        <v>101661</v>
       </c>
     </row>
     <row r="1422">
@@ -18916,10 +18916,10 @@
         </is>
       </c>
       <c r="B1422" s="2" t="n">
-        <v>43160</v>
+        <v>43132</v>
       </c>
       <c r="C1422" t="n">
-        <v>128180</v>
+        <v>110475</v>
       </c>
     </row>
     <row r="1423">
@@ -18929,10 +18929,10 @@
         </is>
       </c>
       <c r="B1423" s="2" t="n">
-        <v>43191</v>
+        <v>43160</v>
       </c>
       <c r="C1423" t="n">
-        <v>116433</v>
+        <v>128180</v>
       </c>
     </row>
     <row r="1424">
@@ -18942,10 +18942,10 @@
         </is>
       </c>
       <c r="B1424" s="2" t="n">
-        <v>43221</v>
+        <v>43191</v>
       </c>
       <c r="C1424" t="n">
-        <v>135525</v>
+        <v>116433</v>
       </c>
     </row>
     <row r="1425">
@@ -18955,10 +18955,10 @@
         </is>
       </c>
       <c r="B1425" s="2" t="n">
-        <v>43252</v>
+        <v>43221</v>
       </c>
       <c r="C1425" t="n">
-        <v>142397</v>
+        <v>135525</v>
       </c>
     </row>
     <row r="1426">
@@ -18968,10 +18968,10 @@
         </is>
       </c>
       <c r="B1426" s="2" t="n">
-        <v>43282</v>
+        <v>43252</v>
       </c>
       <c r="C1426" t="n">
-        <v>131182</v>
+        <v>142397</v>
       </c>
     </row>
     <row r="1427">
@@ -18981,10 +18981,10 @@
         </is>
       </c>
       <c r="B1427" s="2" t="n">
-        <v>43313</v>
+        <v>43282</v>
       </c>
       <c r="C1427" t="n">
-        <v>107692</v>
+        <v>131182</v>
       </c>
     </row>
     <row r="1428">
@@ -18994,10 +18994,10 @@
         </is>
       </c>
       <c r="B1428" s="2" t="n">
-        <v>43344</v>
+        <v>43313</v>
       </c>
       <c r="C1428" t="n">
-        <v>69128</v>
+        <v>107692</v>
       </c>
     </row>
     <row r="1429">
@@ -19007,10 +19007,10 @@
         </is>
       </c>
       <c r="B1429" s="2" t="n">
-        <v>43374</v>
+        <v>43344</v>
       </c>
       <c r="C1429" t="n">
-        <v>88411</v>
+        <v>69128</v>
       </c>
     </row>
     <row r="1430">
@@ -19020,10 +19020,10 @@
         </is>
       </c>
       <c r="B1430" s="2" t="n">
-        <v>43405</v>
+        <v>43374</v>
       </c>
       <c r="C1430" t="n">
-        <v>91063</v>
+        <v>88411</v>
       </c>
     </row>
     <row r="1431">
@@ -19033,10 +19033,10 @@
         </is>
       </c>
       <c r="B1431" s="2" t="n">
-        <v>43435</v>
+        <v>43405</v>
       </c>
       <c r="C1431" t="n">
-        <v>99290</v>
+        <v>91063</v>
       </c>
     </row>
     <row r="1432">
@@ -19046,10 +19046,10 @@
         </is>
       </c>
       <c r="B1432" s="2" t="n">
-        <v>43466</v>
+        <v>43435</v>
       </c>
       <c r="C1432" t="n">
-        <v>93538</v>
+        <v>99290</v>
       </c>
     </row>
     <row r="1433">
@@ -19059,10 +19059,10 @@
         </is>
       </c>
       <c r="B1433" s="2" t="n">
-        <v>43497</v>
+        <v>43466</v>
       </c>
       <c r="C1433" t="n">
-        <v>100693</v>
+        <v>93538</v>
       </c>
     </row>
     <row r="1434">
@@ -19072,10 +19072,10 @@
         </is>
       </c>
       <c r="B1434" s="2" t="n">
-        <v>43525</v>
+        <v>43497</v>
       </c>
       <c r="C1434" t="n">
-        <v>122659</v>
+        <v>100693</v>
       </c>
     </row>
     <row r="1435">
@@ -19085,10 +19085,10 @@
         </is>
       </c>
       <c r="B1435" s="2" t="n">
-        <v>43556</v>
+        <v>43525</v>
       </c>
       <c r="C1435" t="n">
-        <v>119417</v>
+        <v>122659</v>
       </c>
     </row>
     <row r="1436">
@@ -19098,10 +19098,10 @@
         </is>
       </c>
       <c r="B1436" s="2" t="n">
-        <v>43586</v>
+        <v>43556</v>
       </c>
       <c r="C1436" t="n">
-        <v>125623</v>
+        <v>119417</v>
       </c>
     </row>
     <row r="1437">
@@ -19111,10 +19111,10 @@
         </is>
       </c>
       <c r="B1437" s="2" t="n">
-        <v>43617</v>
+        <v>43586</v>
       </c>
       <c r="C1437" t="n">
-        <v>130513</v>
+        <v>125623</v>
       </c>
     </row>
     <row r="1438">
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="B1438" s="2" t="n">
-        <v>43647</v>
+        <v>43617</v>
       </c>
       <c r="C1438" t="n">
-        <v>116673</v>
+        <v>130513</v>
       </c>
     </row>
     <row r="1439">
@@ -19137,10 +19137,10 @@
         </is>
       </c>
       <c r="B1439" s="2" t="n">
-        <v>43678</v>
+        <v>43647</v>
       </c>
       <c r="C1439" t="n">
-        <v>74424</v>
+        <v>116673</v>
       </c>
     </row>
     <row r="1440">
@@ -19150,10 +19150,10 @@
         </is>
       </c>
       <c r="B1440" s="2" t="n">
-        <v>43709</v>
+        <v>43678</v>
       </c>
       <c r="C1440" t="n">
-        <v>81746</v>
+        <v>74424</v>
       </c>
     </row>
     <row r="1441">
@@ -19163,10 +19163,10 @@
         </is>
       </c>
       <c r="B1441" s="2" t="n">
-        <v>43739</v>
+        <v>43709</v>
       </c>
       <c r="C1441" t="n">
-        <v>93954</v>
+        <v>81746</v>
       </c>
     </row>
     <row r="1442">
@@ -19176,10 +19176,10 @@
         </is>
       </c>
       <c r="B1442" s="2" t="n">
-        <v>43770</v>
+        <v>43739</v>
       </c>
       <c r="C1442" t="n">
-        <v>93155</v>
+        <v>93954</v>
       </c>
     </row>
     <row r="1443">
@@ -19189,10 +19189,10 @@
         </is>
       </c>
       <c r="B1443" s="2" t="n">
-        <v>43800</v>
+        <v>43770</v>
       </c>
       <c r="C1443" t="n">
-        <v>105854</v>
+        <v>93155</v>
       </c>
     </row>
     <row r="1444">
@@ -19202,10 +19202,10 @@
         </is>
       </c>
       <c r="B1444" s="2" t="n">
-        <v>43831</v>
+        <v>43800</v>
       </c>
       <c r="C1444" t="n">
-        <v>86442</v>
+        <v>105854</v>
       </c>
     </row>
     <row r="1445">
@@ -19215,10 +19215,10 @@
         </is>
       </c>
       <c r="B1445" s="2" t="n">
-        <v>43862</v>
+        <v>43831</v>
       </c>
       <c r="C1445" t="n">
-        <v>94618</v>
+        <v>86442</v>
       </c>
     </row>
     <row r="1446">
@@ -19228,10 +19228,10 @@
         </is>
       </c>
       <c r="B1446" s="2" t="n">
-        <v>43891</v>
+        <v>43862</v>
       </c>
       <c r="C1446" t="n">
-        <v>37643</v>
+        <v>94618</v>
       </c>
     </row>
     <row r="1447">
@@ -19241,10 +19241,10 @@
         </is>
       </c>
       <c r="B1447" s="2" t="n">
-        <v>43922</v>
+        <v>43891</v>
       </c>
       <c r="C1447" t="n">
-        <v>4163</v>
+        <v>37643</v>
       </c>
     </row>
     <row r="1448">
@@ -19254,10 +19254,10 @@
         </is>
       </c>
       <c r="B1448" s="2" t="n">
-        <v>43952</v>
+        <v>43922</v>
       </c>
       <c r="C1448" t="n">
-        <v>34338</v>
+        <v>4163</v>
       </c>
     </row>
     <row r="1449">
@@ -19267,10 +19267,10 @@
         </is>
       </c>
       <c r="B1449" s="2" t="n">
-        <v>43983</v>
+        <v>43952</v>
       </c>
       <c r="C1449" t="n">
-        <v>82651</v>
+        <v>34338</v>
       </c>
     </row>
     <row r="1450">
@@ -19280,10 +19280,10 @@
         </is>
       </c>
       <c r="B1450" s="2" t="n">
-        <v>44013</v>
+        <v>43983</v>
       </c>
       <c r="C1450" t="n">
-        <v>117930</v>
+        <v>82651</v>
       </c>
     </row>
     <row r="1451">
@@ -19293,10 +19293,10 @@
         </is>
       </c>
       <c r="B1451" s="2" t="n">
-        <v>44044</v>
+        <v>44013</v>
       </c>
       <c r="C1451" t="n">
-        <v>66923</v>
+        <v>117930</v>
       </c>
     </row>
     <row r="1452">
@@ -19306,10 +19306,10 @@
         </is>
       </c>
       <c r="B1452" s="2" t="n">
-        <v>44075</v>
+        <v>44044</v>
       </c>
       <c r="C1452" t="n">
-        <v>70728</v>
+        <v>66923</v>
       </c>
     </row>
     <row r="1453">
@@ -19319,10 +19319,10 @@
         </is>
       </c>
       <c r="B1453" s="2" t="n">
-        <v>44105</v>
+        <v>44075</v>
       </c>
       <c r="C1453" t="n">
-        <v>74228</v>
+        <v>70728</v>
       </c>
     </row>
     <row r="1454">
@@ -19332,10 +19332,10 @@
         </is>
       </c>
       <c r="B1454" s="2" t="n">
-        <v>44136</v>
+        <v>44105</v>
       </c>
       <c r="C1454" t="n">
-        <v>75706</v>
+        <v>74228</v>
       </c>
     </row>
     <row r="1455">
@@ -19345,10 +19345,10 @@
         </is>
       </c>
       <c r="B1455" s="2" t="n">
-        <v>44166</v>
+        <v>44136</v>
       </c>
       <c r="C1455" t="n">
-        <v>105840</v>
+        <v>75706</v>
       </c>
     </row>
     <row r="1456">
@@ -19358,10 +19358,10 @@
         </is>
       </c>
       <c r="B1456" s="2" t="n">
-        <v>44197</v>
+        <v>44166</v>
       </c>
       <c r="C1456" t="n">
-        <v>41966</v>
+        <v>105840</v>
       </c>
     </row>
     <row r="1457">
@@ -19371,10 +19371,10 @@
         </is>
       </c>
       <c r="B1457" s="2" t="n">
-        <v>44228</v>
+        <v>44197</v>
       </c>
       <c r="C1457" t="n">
-        <v>58277</v>
+        <v>41966</v>
       </c>
     </row>
     <row r="1458">
@@ -19384,10 +19384,10 @@
         </is>
       </c>
       <c r="B1458" s="2" t="n">
-        <v>44256</v>
+        <v>44228</v>
       </c>
       <c r="C1458" t="n">
-        <v>85817</v>
+        <v>58277</v>
       </c>
     </row>
     <row r="1459">
@@ -19397,10 +19397,10 @@
         </is>
       </c>
       <c r="B1459" s="2" t="n">
-        <v>44287</v>
+        <v>44256</v>
       </c>
       <c r="C1459" t="n">
-        <v>78594</v>
+        <v>85817</v>
       </c>
     </row>
     <row r="1460">
@@ -19410,10 +19410,10 @@
         </is>
       </c>
       <c r="B1460" s="2" t="n">
-        <v>44317</v>
+        <v>44287</v>
       </c>
       <c r="C1460" t="n">
-        <v>95399</v>
+        <v>78594</v>
       </c>
     </row>
     <row r="1461">
@@ -19423,10 +19423,10 @@
         </is>
       </c>
       <c r="B1461" s="2" t="n">
-        <v>44348</v>
+        <v>44317</v>
       </c>
       <c r="C1461" t="n">
-        <v>96784</v>
+        <v>95399</v>
       </c>
     </row>
     <row r="1462">
@@ -19436,10 +19436,10 @@
         </is>
       </c>
       <c r="B1462" s="2" t="n">
-        <v>44378</v>
+        <v>44348</v>
       </c>
       <c r="C1462" t="n">
-        <v>83898</v>
+        <v>96784</v>
       </c>
     </row>
     <row r="1463">
@@ -19449,10 +19449,10 @@
         </is>
       </c>
       <c r="B1463" s="2" t="n">
-        <v>44409</v>
+        <v>44378</v>
       </c>
       <c r="C1463" t="n">
-        <v>47583</v>
+        <v>83898</v>
       </c>
     </row>
     <row r="1464">
@@ -19462,10 +19462,10 @@
         </is>
       </c>
       <c r="B1464" s="2" t="n">
-        <v>44440</v>
+        <v>44409</v>
       </c>
       <c r="C1464" t="n">
-        <v>59641</v>
+        <v>47583</v>
       </c>
     </row>
     <row r="1465">
@@ -19475,10 +19475,10 @@
         </is>
       </c>
       <c r="B1465" s="2" t="n">
-        <v>44470</v>
+        <v>44440</v>
       </c>
       <c r="C1465" t="n">
-        <v>59044</v>
+        <v>59641</v>
       </c>
     </row>
     <row r="1466">
@@ -19488,10 +19488,10 @@
         </is>
       </c>
       <c r="B1466" s="2" t="n">
-        <v>44501</v>
+        <v>44470</v>
       </c>
       <c r="C1466" t="n">
-        <v>66399</v>
+        <v>59044</v>
       </c>
     </row>
     <row r="1467">
@@ -19501,10 +19501,10 @@
         </is>
       </c>
       <c r="B1467" s="2" t="n">
-        <v>44531</v>
+        <v>44501</v>
       </c>
       <c r="C1467" t="n">
-        <v>86081</v>
+        <v>66399</v>
       </c>
     </row>
     <row r="1468">
@@ -19514,10 +19514,10 @@
         </is>
       </c>
       <c r="B1468" s="2" t="n">
-        <v>44562</v>
+        <v>44531</v>
       </c>
       <c r="C1468" t="n">
-        <v>42377</v>
+        <v>86081</v>
       </c>
     </row>
     <row r="1469">
@@ -19527,10 +19527,10 @@
         </is>
       </c>
       <c r="B1469" s="2" t="n">
-        <v>44593</v>
+        <v>44562</v>
       </c>
       <c r="C1469" t="n">
-        <v>62102</v>
+        <v>42377</v>
       </c>
     </row>
     <row r="1470">
@@ -19540,10 +19540,10 @@
         </is>
       </c>
       <c r="B1470" s="2" t="n">
-        <v>44621</v>
+        <v>44593</v>
       </c>
       <c r="C1470" t="n">
-        <v>59920</v>
+        <v>62102</v>
       </c>
     </row>
     <row r="1471">
@@ -19553,10 +19553,10 @@
         </is>
       </c>
       <c r="B1471" s="2" t="n">
-        <v>44652</v>
+        <v>44621</v>
       </c>
       <c r="C1471" t="n">
-        <v>69111</v>
+        <v>59920</v>
       </c>
     </row>
     <row r="1472">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="B1472" s="2" t="n">
-        <v>44682</v>
+        <v>44652</v>
       </c>
       <c r="C1472" t="n">
-        <v>84977</v>
+        <v>69111</v>
       </c>
     </row>
     <row r="1473">
@@ -19579,10 +19579,10 @@
         </is>
       </c>
       <c r="B1473" s="2" t="n">
-        <v>44713</v>
+        <v>44682</v>
       </c>
       <c r="C1473" t="n">
-        <v>89252</v>
+        <v>84977</v>
       </c>
     </row>
     <row r="1474">
@@ -19592,10 +19592,10 @@
         </is>
       </c>
       <c r="B1474" s="2" t="n">
-        <v>44743</v>
+        <v>44713</v>
       </c>
       <c r="C1474" t="n">
-        <v>73378</v>
+        <v>89252</v>
       </c>
     </row>
     <row r="1475">
@@ -19605,10 +19605,10 @@
         </is>
       </c>
       <c r="B1475" s="2" t="n">
-        <v>44774</v>
+        <v>44743</v>
       </c>
       <c r="C1475" t="n">
-        <v>51907</v>
+        <v>73378</v>
       </c>
     </row>
     <row r="1476">
@@ -19618,10 +19618,10 @@
         </is>
       </c>
       <c r="B1476" s="2" t="n">
-        <v>44805</v>
+        <v>44774</v>
       </c>
       <c r="C1476" t="n">
-        <v>67240</v>
+        <v>51907</v>
       </c>
     </row>
     <row r="1477">
@@ -19631,10 +19631,10 @@
         </is>
       </c>
       <c r="B1477" s="2" t="n">
-        <v>44835</v>
+        <v>44805</v>
       </c>
       <c r="C1477" t="n">
-        <v>65966</v>
+        <v>67240</v>
       </c>
     </row>
     <row r="1478">
@@ -19644,10 +19644,10 @@
         </is>
       </c>
       <c r="B1478" s="2" t="n">
-        <v>44866</v>
+        <v>44835</v>
       </c>
       <c r="C1478" t="n">
-        <v>73221</v>
+        <v>65966</v>
       </c>
     </row>
     <row r="1479">
@@ -19657,10 +19657,10 @@
         </is>
       </c>
       <c r="B1479" s="2" t="n">
-        <v>44896</v>
+        <v>44866</v>
       </c>
       <c r="C1479" t="n">
-        <v>73927</v>
+        <v>73221</v>
       </c>
     </row>
     <row r="1480">
@@ -19670,10 +19670,10 @@
         </is>
       </c>
       <c r="B1480" s="2" t="n">
-        <v>44927</v>
+        <v>44896</v>
       </c>
       <c r="C1480" t="n">
-        <v>64147</v>
+        <v>73927</v>
       </c>
     </row>
     <row r="1481">
@@ -19683,10 +19683,10 @@
         </is>
       </c>
       <c r="B1481" s="2" t="n">
-        <v>44958</v>
+        <v>44927</v>
       </c>
       <c r="C1481" t="n">
-        <v>74001</v>
+        <v>64147</v>
       </c>
     </row>
     <row r="1482">
@@ -19696,10 +19696,10 @@
         </is>
       </c>
       <c r="B1482" s="2" t="n">
-        <v>44986</v>
+        <v>44958</v>
       </c>
       <c r="C1482" t="n">
-        <v>99524</v>
+        <v>74001</v>
       </c>
     </row>
     <row r="1483">
@@ -19709,10 +19709,10 @@
         </is>
       </c>
       <c r="B1483" s="2" t="n">
-        <v>45017</v>
+        <v>44986</v>
       </c>
       <c r="C1483" t="n">
-        <v>74749</v>
+        <v>99524</v>
       </c>
     </row>
     <row r="1484">
@@ -19722,10 +19722,10 @@
         </is>
       </c>
       <c r="B1484" s="2" t="n">
-        <v>45047</v>
+        <v>45017</v>
       </c>
       <c r="C1484" t="n">
-        <v>92025</v>
+        <v>74749</v>
       </c>
     </row>
     <row r="1485">
@@ -19735,10 +19735,10 @@
         </is>
       </c>
       <c r="B1485" s="2" t="n">
-        <v>45078</v>
+        <v>45047</v>
       </c>
       <c r="C1485" t="n">
-        <v>101085</v>
+        <v>92025</v>
       </c>
     </row>
     <row r="1486">
@@ -19748,10 +19748,10 @@
         </is>
       </c>
       <c r="B1486" s="2" t="n">
-        <v>45108</v>
+        <v>45078</v>
       </c>
       <c r="C1486" t="n">
-        <v>81205</v>
+        <v>101085</v>
       </c>
     </row>
     <row r="1487">
@@ -19761,10 +19761,10 @@
         </is>
       </c>
       <c r="B1487" s="2" t="n">
-        <v>45139</v>
+        <v>45108</v>
       </c>
       <c r="C1487" t="n">
-        <v>55954</v>
+        <v>81205</v>
       </c>
     </row>
     <row r="1488">
@@ -19774,10 +19774,10 @@
         </is>
       </c>
       <c r="B1488" s="2" t="n">
-        <v>45170</v>
+        <v>45139</v>
       </c>
       <c r="C1488" t="n">
-        <v>68803</v>
+        <v>55954</v>
       </c>
     </row>
     <row r="1489">
@@ -19787,10 +19787,10 @@
         </is>
       </c>
       <c r="B1489" s="2" t="n">
-        <v>45200</v>
+        <v>45170</v>
       </c>
       <c r="C1489" t="n">
-        <v>77892</v>
+        <v>68803</v>
       </c>
     </row>
     <row r="1490">
@@ -19800,10 +19800,10 @@
         </is>
       </c>
       <c r="B1490" s="2" t="n">
-        <v>45231</v>
+        <v>45200</v>
       </c>
       <c r="C1490" t="n">
-        <v>78314</v>
+        <v>77892</v>
       </c>
     </row>
     <row r="1491">
@@ -19813,10 +19813,10 @@
         </is>
       </c>
       <c r="B1491" s="2" t="n">
-        <v>45261</v>
+        <v>45231</v>
       </c>
       <c r="C1491" t="n">
-        <v>81772</v>
+        <v>78314</v>
       </c>
     </row>
     <row r="1492">
@@ -19826,10 +19826,10 @@
         </is>
       </c>
       <c r="B1492" s="2" t="n">
-        <v>45292</v>
+        <v>45261</v>
       </c>
       <c r="C1492" t="n">
-        <v>68688</v>
+        <v>81772</v>
       </c>
     </row>
     <row r="1493">
@@ -19839,10 +19839,10 @@
         </is>
       </c>
       <c r="B1493" s="2" t="n">
-        <v>45323</v>
+        <v>45292</v>
       </c>
       <c r="C1493" t="n">
-        <v>81348</v>
+        <v>68688</v>
       </c>
     </row>
     <row r="1494">
@@ -19852,10 +19852,10 @@
         </is>
       </c>
       <c r="B1494" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
       <c r="C1494" t="n">
-        <v>94699</v>
+        <v>81348</v>
       </c>
     </row>
     <row r="1495">
@@ -19865,10 +19865,10 @@
         </is>
       </c>
       <c r="B1495" s="2" t="n">
-        <v>45383</v>
+        <v>45352</v>
       </c>
       <c r="C1495" t="n">
-        <v>92004</v>
+        <v>94699</v>
       </c>
     </row>
     <row r="1496">
@@ -19878,10 +19878,10 @@
         </is>
       </c>
       <c r="B1496" s="2" t="n">
-        <v>45413</v>
+        <v>45383</v>
       </c>
       <c r="C1496" t="n">
-        <v>95164</v>
+        <v>92004</v>
       </c>
     </row>
     <row r="1497">
@@ -19891,10 +19891,10 @@
         </is>
       </c>
       <c r="B1497" s="2" t="n">
-        <v>45444</v>
+        <v>45413</v>
       </c>
       <c r="C1497" t="n">
-        <v>103371</v>
+        <v>95164</v>
       </c>
     </row>
     <row r="1498">
@@ -19904,10 +19904,10 @@
         </is>
       </c>
       <c r="B1498" s="2" t="n">
-        <v>45474</v>
+        <v>45444</v>
       </c>
       <c r="C1498" t="n">
-        <v>83983</v>
+        <v>103371</v>
       </c>
     </row>
     <row r="1499">
@@ -19917,10 +19917,10 @@
         </is>
       </c>
       <c r="B1499" s="2" t="n">
-        <v>45505</v>
+        <v>45474</v>
       </c>
       <c r="C1499" t="n">
-        <v>52322</v>
+        <v>83983</v>
       </c>
     </row>
     <row r="1500">
@@ -19930,10 +19930,10 @@
         </is>
       </c>
       <c r="B1500" s="2" t="n">
-        <v>45536</v>
+        <v>45505</v>
       </c>
       <c r="C1500" t="n">
-        <v>73146</v>
+        <v>52322</v>
       </c>
     </row>
     <row r="1501">
@@ -19943,10 +19943,10 @@
         </is>
       </c>
       <c r="B1501" s="2" t="n">
-        <v>45566</v>
+        <v>45536</v>
       </c>
       <c r="C1501" t="n">
-        <v>83479</v>
+        <v>73146</v>
       </c>
     </row>
     <row r="1502">
@@ -19956,10 +19956,10 @@
         </is>
       </c>
       <c r="B1502" s="2" t="n">
-        <v>45597</v>
+        <v>45566</v>
       </c>
       <c r="C1502" t="n">
-        <v>83362</v>
+        <v>83479</v>
       </c>
     </row>
     <row r="1503">
@@ -19969,10 +19969,10 @@
         </is>
       </c>
       <c r="B1503" s="2" t="n">
-        <v>45627</v>
+        <v>45597</v>
       </c>
       <c r="C1503" t="n">
-        <v>105364</v>
+        <v>83362</v>
       </c>
     </row>
     <row r="1504">
@@ -19982,10 +19982,10 @@
         </is>
       </c>
       <c r="B1504" s="2" t="n">
-        <v>45658</v>
+        <v>45627</v>
       </c>
       <c r="C1504" t="n">
-        <v>72334</v>
+        <v>105364</v>
       </c>
     </row>
     <row r="1505">
@@ -19995,10 +19995,10 @@
         </is>
       </c>
       <c r="B1505" s="2" t="n">
-        <v>45689</v>
+        <v>45658</v>
       </c>
       <c r="C1505" t="n">
-        <v>90342</v>
+        <v>72334</v>
       </c>
     </row>
     <row r="1506">
@@ -20008,10 +20008,10 @@
         </is>
       </c>
       <c r="B1506" s="2" t="n">
-        <v>45717</v>
+        <v>45689</v>
       </c>
       <c r="C1506" t="n">
-        <v>116733</v>
+        <v>90342</v>
       </c>
     </row>
     <row r="1507">
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="B1507" s="2" t="n">
-        <v>45748</v>
+        <v>45717</v>
       </c>
       <c r="C1507" t="n">
-        <v>98549</v>
+        <v>116733</v>
       </c>
     </row>
     <row r="1508">
@@ -20034,10 +20034,10 @@
         </is>
       </c>
       <c r="B1508" s="2" t="n">
-        <v>45778</v>
+        <v>45748</v>
       </c>
       <c r="C1508" t="n">
-        <v>112811</v>
+        <v>98549</v>
       </c>
     </row>
     <row r="1509">
@@ -20047,10 +20047,10 @@
         </is>
       </c>
       <c r="B1509" s="2" t="n">
-        <v>45809</v>
+        <v>45778</v>
       </c>
       <c r="C1509" t="n">
-        <v>119145</v>
+        <v>112811</v>
       </c>
     </row>
     <row r="1510">
@@ -20060,10 +20060,10 @@
         </is>
       </c>
       <c r="B1510" s="2" t="n">
-        <v>45839</v>
+        <v>45809</v>
       </c>
       <c r="C1510" t="n">
-        <v>98335</v>
+        <v>119145</v>
       </c>
     </row>
     <row r="1511">
@@ -20073,10 +20073,10 @@
         </is>
       </c>
       <c r="B1511" s="2" t="n">
-        <v>45870</v>
+        <v>45839</v>
       </c>
       <c r="C1511" t="n">
-        <v>61315</v>
+        <v>98335</v>
       </c>
     </row>
     <row r="1512">
@@ -20086,10 +20086,10 @@
         </is>
       </c>
       <c r="B1512" s="2" t="n">
-        <v>45901</v>
+        <v>45870</v>
       </c>
       <c r="C1512" t="n">
-        <v>85167</v>
+        <v>61315</v>
       </c>
     </row>
     <row r="1513">
@@ -20099,10 +20099,10 @@
         </is>
       </c>
       <c r="B1513" s="2" t="n">
-        <v>45931</v>
+        <v>45901</v>
       </c>
       <c r="C1513" t="n">
-        <v>96784</v>
+        <v>85167</v>
       </c>
     </row>
     <row r="1514">
@@ -20112,10 +20112,10 @@
         </is>
       </c>
       <c r="B1514" s="2" t="n">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="C1514" t="n">
-        <v>94124</v>
+        <v>96784</v>
       </c>
     </row>
     <row r="1515">
@@ -20125,10 +20125,10 @@
         </is>
       </c>
       <c r="B1515" s="2" t="n">
-        <v>45992</v>
+        <v>45962</v>
       </c>
       <c r="C1515" t="n">
-        <v>103011</v>
+        <v>94124</v>
       </c>
     </row>
     <row r="1516">
@@ -20138,10 +20138,10 @@
         </is>
       </c>
       <c r="B1516" s="2" t="n">
-        <v>46023</v>
+        <v>45992</v>
       </c>
       <c r="C1516" t="n">
-        <v>73105</v>
+        <v>103011</v>
       </c>
     </row>
     <row r="1517">
@@ -20151,10 +20151,10 @@
         </is>
       </c>
       <c r="B1517" s="2" t="n">
-        <v>46054</v>
+        <v>46023</v>
       </c>
       <c r="C1517" t="n">
-        <v>97083</v>
+        <v>73105</v>
       </c>
     </row>
     <row r="1518">
@@ -20164,10 +20164,10 @@
         </is>
       </c>
       <c r="B1518" s="2" t="n">
-        <v>46082</v>
+        <v>46054</v>
       </c>
       <c r="C1518" t="n">
-        <v>130339</v>
+        <v>97083</v>
       </c>
     </row>
     <row r="1519">
@@ -20177,10 +20177,10 @@
         </is>
       </c>
       <c r="B1519" s="2" t="n">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="C1519" t="n">
-        <v>106862</v>
+        <v>130339</v>
       </c>
     </row>
     <row r="1520">
@@ -20190,10 +20190,10 @@
         </is>
       </c>
       <c r="B1520" s="2" t="n">
-        <v>46143</v>
+        <v>46113</v>
       </c>
       <c r="C1520" t="n">
-        <v>111895</v>
+        <v>106862</v>
       </c>
     </row>
     <row r="1521">
@@ -20203,10 +20203,10 @@
         </is>
       </c>
       <c r="B1521" s="2" t="n">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="C1521" t="n">
-        <v>128423</v>
+        <v>111895</v>
       </c>
     </row>
     <row r="1522">
@@ -20216,10 +20216,10 @@
         </is>
       </c>
       <c r="B1522" s="2" t="n">
-        <v>46204</v>
+        <v>46174</v>
       </c>
       <c r="C1522" t="n">
-        <v>101949</v>
+        <v>128423</v>
       </c>
     </row>
     <row r="1523">
@@ -20229,36 +20229,36 @@
         </is>
       </c>
       <c r="B1523" s="2" t="n">
-        <v>46235</v>
+        <v>46204</v>
       </c>
       <c r="C1523" t="n">
-        <v>68544</v>
+        <v>101949</v>
       </c>
     </row>
     <row r="1524">
       <c r="A1524" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B1524" s="2" t="n">
-        <v>42401</v>
+        <v>46235</v>
       </c>
       <c r="C1524" t="n">
-        <v>57093</v>
+        <v>68544</v>
       </c>
     </row>
     <row r="1525">
       <c r="A1525" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B1525" s="2" t="n">
-        <v>42430</v>
+        <v>46266</v>
       </c>
       <c r="C1525" t="n">
-        <v>72646</v>
+        <v>93854</v>
       </c>
     </row>
     <row r="1526">
@@ -20268,10 +20268,10 @@
         </is>
       </c>
       <c r="B1526" s="2" t="n">
-        <v>42461</v>
+        <v>42401</v>
       </c>
       <c r="C1526" t="n">
-        <v>54986</v>
+        <v>57093</v>
       </c>
     </row>
     <row r="1527">
@@ -20281,10 +20281,10 @@
         </is>
       </c>
       <c r="B1527" s="2" t="n">
-        <v>42491</v>
+        <v>42430</v>
       </c>
       <c r="C1527" t="n">
-        <v>66035</v>
+        <v>72646</v>
       </c>
     </row>
     <row r="1528">
@@ -20294,10 +20294,10 @@
         </is>
       </c>
       <c r="B1528" s="2" t="n">
-        <v>42522</v>
+        <v>42461</v>
       </c>
       <c r="C1528" t="n">
-        <v>66049</v>
+        <v>54986</v>
       </c>
     </row>
     <row r="1529">
@@ -20307,10 +20307,10 @@
         </is>
       </c>
       <c r="B1529" s="2" t="n">
-        <v>42552</v>
+        <v>42491</v>
       </c>
       <c r="C1529" t="n">
-        <v>60635</v>
+        <v>66035</v>
       </c>
     </row>
     <row r="1530">
@@ -20320,10 +20320,10 @@
         </is>
       </c>
       <c r="B1530" s="2" t="n">
-        <v>42583</v>
+        <v>42522</v>
       </c>
       <c r="C1530" t="n">
-        <v>63619</v>
+        <v>66049</v>
       </c>
     </row>
     <row r="1531">
@@ -20333,10 +20333,10 @@
         </is>
       </c>
       <c r="B1531" s="2" t="n">
-        <v>42614</v>
+        <v>42552</v>
       </c>
       <c r="C1531" t="n">
-        <v>63641</v>
+        <v>60635</v>
       </c>
     </row>
     <row r="1532">
@@ -20346,10 +20346,10 @@
         </is>
       </c>
       <c r="B1532" s="2" t="n">
-        <v>42644</v>
+        <v>42583</v>
       </c>
       <c r="C1532" t="n">
-        <v>60634</v>
+        <v>63619</v>
       </c>
     </row>
     <row r="1533">
@@ -20359,10 +20359,10 @@
         </is>
       </c>
       <c r="B1533" s="2" t="n">
-        <v>42675</v>
+        <v>42614</v>
       </c>
       <c r="C1533" t="n">
-        <v>64771</v>
+        <v>63641</v>
       </c>
     </row>
     <row r="1534">
@@ -20372,10 +20372,10 @@
         </is>
       </c>
       <c r="B1534" s="2" t="n">
-        <v>42705</v>
+        <v>42644</v>
       </c>
       <c r="C1534" t="n">
-        <v>86858</v>
+        <v>60634</v>
       </c>
     </row>
     <row r="1535">
@@ -20385,10 +20385,10 @@
         </is>
       </c>
       <c r="B1535" s="2" t="n">
-        <v>42736</v>
+        <v>42675</v>
       </c>
       <c r="C1535" t="n">
-        <v>57254</v>
+        <v>64771</v>
       </c>
     </row>
     <row r="1536">
@@ -20398,10 +20398,10 @@
         </is>
       </c>
       <c r="B1536" s="2" t="n">
-        <v>42767</v>
+        <v>42705</v>
       </c>
       <c r="C1536" t="n">
-        <v>68435</v>
+        <v>86858</v>
       </c>
     </row>
     <row r="1537">
@@ -20411,10 +20411,10 @@
         </is>
       </c>
       <c r="B1537" s="2" t="n">
-        <v>42795</v>
+        <v>42736</v>
       </c>
       <c r="C1537" t="n">
-        <v>84801</v>
+        <v>57254</v>
       </c>
     </row>
     <row r="1538">
@@ -20424,10 +20424,10 @@
         </is>
       </c>
       <c r="B1538" s="2" t="n">
-        <v>42826</v>
+        <v>42767</v>
       </c>
       <c r="C1538" t="n">
-        <v>63267</v>
+        <v>68435</v>
       </c>
     </row>
     <row r="1539">
@@ -20437,10 +20437,10 @@
         </is>
       </c>
       <c r="B1539" s="2" t="n">
-        <v>42856</v>
+        <v>42795</v>
       </c>
       <c r="C1539" t="n">
-        <v>66425</v>
+        <v>84801</v>
       </c>
     </row>
     <row r="1540">
@@ -20450,10 +20450,10 @@
         </is>
       </c>
       <c r="B1540" s="2" t="n">
-        <v>42887</v>
+        <v>42826</v>
       </c>
       <c r="C1540" t="n">
-        <v>69798</v>
+        <v>63267</v>
       </c>
     </row>
     <row r="1541">
@@ -20463,10 +20463,10 @@
         </is>
       </c>
       <c r="B1541" s="2" t="n">
-        <v>42917</v>
+        <v>42856</v>
       </c>
       <c r="C1541" t="n">
-        <v>65178</v>
+        <v>66425</v>
       </c>
     </row>
     <row r="1542">
@@ -20476,10 +20476,10 @@
         </is>
       </c>
       <c r="B1542" s="2" t="n">
-        <v>42948</v>
+        <v>42887</v>
       </c>
       <c r="C1542" t="n">
-        <v>67965</v>
+        <v>69798</v>
       </c>
     </row>
     <row r="1543">
@@ -20489,10 +20489,10 @@
         </is>
       </c>
       <c r="B1543" s="2" t="n">
-        <v>42979</v>
+        <v>42917</v>
       </c>
       <c r="C1543" t="n">
-        <v>77592</v>
+        <v>65178</v>
       </c>
     </row>
     <row r="1544">
@@ -20502,10 +20502,10 @@
         </is>
       </c>
       <c r="B1544" s="2" t="n">
-        <v>43009</v>
+        <v>42948</v>
       </c>
       <c r="C1544" t="n">
-        <v>68551</v>
+        <v>67965</v>
       </c>
     </row>
     <row r="1545">
@@ -20515,10 +20515,10 @@
         </is>
       </c>
       <c r="B1545" s="2" t="n">
-        <v>43040</v>
+        <v>42979</v>
       </c>
       <c r="C1545" t="n">
-        <v>78082</v>
+        <v>77592</v>
       </c>
     </row>
     <row r="1546">
@@ -20528,10 +20528,10 @@
         </is>
       </c>
       <c r="B1546" s="2" t="n">
-        <v>43070</v>
+        <v>43009</v>
       </c>
       <c r="C1546" t="n">
-        <v>104302</v>
+        <v>68551</v>
       </c>
     </row>
     <row r="1547">
@@ -20541,10 +20541,10 @@
         </is>
       </c>
       <c r="B1547" s="2" t="n">
-        <v>43101</v>
+        <v>43040</v>
       </c>
       <c r="C1547" t="n">
-        <v>66545</v>
+        <v>78082</v>
       </c>
     </row>
     <row r="1548">
@@ -20554,10 +20554,10 @@
         </is>
       </c>
       <c r="B1548" s="2" t="n">
-        <v>43132</v>
+        <v>43070</v>
       </c>
       <c r="C1548" t="n">
-        <v>75466</v>
+        <v>104302</v>
       </c>
     </row>
     <row r="1549">
@@ -20567,10 +20567,10 @@
         </is>
       </c>
       <c r="B1549" s="2" t="n">
-        <v>43160</v>
+        <v>43101</v>
       </c>
       <c r="C1549" t="n">
-        <v>95082</v>
+        <v>66545</v>
       </c>
     </row>
     <row r="1550">
@@ -20580,10 +20580,10 @@
         </is>
       </c>
       <c r="B1550" s="2" t="n">
-        <v>43191</v>
+        <v>43132</v>
       </c>
       <c r="C1550" t="n">
-        <v>79206</v>
+        <v>75466</v>
       </c>
     </row>
     <row r="1551">
@@ -20593,10 +20593,10 @@
         </is>
       </c>
       <c r="B1551" s="2" t="n">
-        <v>43221</v>
+        <v>43160</v>
       </c>
       <c r="C1551" t="n">
-        <v>84965</v>
+        <v>95082</v>
       </c>
     </row>
     <row r="1552">
@@ -20606,10 +20606,10 @@
         </is>
       </c>
       <c r="B1552" s="2" t="n">
-        <v>43252</v>
+        <v>43191</v>
       </c>
       <c r="C1552" t="n">
-        <v>87854</v>
+        <v>79206</v>
       </c>
     </row>
     <row r="1553">
@@ -20619,10 +20619,10 @@
         </is>
       </c>
       <c r="B1553" s="2" t="n">
-        <v>43282</v>
+        <v>43221</v>
       </c>
       <c r="C1553" t="n">
-        <v>81946</v>
+        <v>84965</v>
       </c>
     </row>
     <row r="1554">
@@ -20632,10 +20632,10 @@
         </is>
       </c>
       <c r="B1554" s="2" t="n">
-        <v>43313</v>
+        <v>43252</v>
       </c>
       <c r="C1554" t="n">
-        <v>86814</v>
+        <v>87854</v>
       </c>
     </row>
     <row r="1555">
@@ -20645,10 +20645,10 @@
         </is>
       </c>
       <c r="B1555" s="2" t="n">
-        <v>43344</v>
+        <v>43282</v>
       </c>
       <c r="C1555" t="n">
-        <v>88706</v>
+        <v>81946</v>
       </c>
     </row>
     <row r="1556">
@@ -20658,10 +20658,10 @@
         </is>
       </c>
       <c r="B1556" s="2" t="n">
-        <v>43374</v>
+        <v>43313</v>
       </c>
       <c r="C1556" t="n">
-        <v>86931</v>
+        <v>86814</v>
       </c>
     </row>
     <row r="1557">
@@ -20671,10 +20671,10 @@
         </is>
       </c>
       <c r="B1557" s="2" t="n">
-        <v>43405</v>
+        <v>43344</v>
       </c>
       <c r="C1557" t="n">
-        <v>94643</v>
+        <v>88706</v>
       </c>
     </row>
     <row r="1558">
@@ -20684,10 +20684,10 @@
         </is>
       </c>
       <c r="B1558" s="2" t="n">
-        <v>43435</v>
+        <v>43374</v>
       </c>
       <c r="C1558" t="n">
-        <v>113581</v>
+        <v>86931</v>
       </c>
     </row>
     <row r="1559">
@@ -20697,10 +20697,10 @@
         </is>
       </c>
       <c r="B1559" s="2" t="n">
-        <v>43466</v>
+        <v>43405</v>
       </c>
       <c r="C1559" t="n">
-        <v>78061</v>
+        <v>94643</v>
       </c>
     </row>
     <row r="1560">
@@ -20710,10 +20710,10 @@
         </is>
       </c>
       <c r="B1560" s="2" t="n">
-        <v>43497</v>
+        <v>43435</v>
       </c>
       <c r="C1560" t="n">
-        <v>82324</v>
+        <v>113581</v>
       </c>
     </row>
     <row r="1561">
@@ -20723,10 +20723,10 @@
         </is>
       </c>
       <c r="B1561" s="2" t="n">
-        <v>43525</v>
+        <v>43466</v>
       </c>
       <c r="C1561" t="n">
-        <v>103164</v>
+        <v>78061</v>
       </c>
     </row>
     <row r="1562">
@@ -20736,10 +20736,10 @@
         </is>
       </c>
       <c r="B1562" s="2" t="n">
-        <v>43556</v>
+        <v>43497</v>
       </c>
       <c r="C1562" t="n">
-        <v>86076</v>
+        <v>82324</v>
       </c>
     </row>
     <row r="1563">
@@ -20749,10 +20749,10 @@
         </is>
       </c>
       <c r="B1563" s="2" t="n">
-        <v>43586</v>
+        <v>43525</v>
       </c>
       <c r="C1563" t="n">
-        <v>88097</v>
+        <v>103164</v>
       </c>
     </row>
     <row r="1564">
@@ -20762,10 +20762,10 @@
         </is>
       </c>
       <c r="B1564" s="2" t="n">
-        <v>43617</v>
+        <v>43556</v>
       </c>
       <c r="C1564" t="n">
-        <v>86048</v>
+        <v>86076</v>
       </c>
     </row>
     <row r="1565">
@@ -20775,10 +20775,10 @@
         </is>
       </c>
       <c r="B1565" s="2" t="n">
-        <v>43647</v>
+        <v>43586</v>
       </c>
       <c r="C1565" t="n">
-        <v>81044</v>
+        <v>88097</v>
       </c>
     </row>
     <row r="1566">
@@ -20788,10 +20788,10 @@
         </is>
       </c>
       <c r="B1566" s="2" t="n">
-        <v>43678</v>
+        <v>43617</v>
       </c>
       <c r="C1566" t="n">
-        <v>80838</v>
+        <v>86048</v>
       </c>
     </row>
     <row r="1567">
@@ -20801,10 +20801,10 @@
         </is>
       </c>
       <c r="B1567" s="2" t="n">
-        <v>43709</v>
+        <v>43647</v>
       </c>
       <c r="C1567" t="n">
-        <v>76195</v>
+        <v>81044</v>
       </c>
     </row>
     <row r="1568">
@@ -20814,10 +20814,10 @@
         </is>
       </c>
       <c r="B1568" s="2" t="n">
-        <v>43739</v>
+        <v>43678</v>
       </c>
       <c r="C1568" t="n">
-        <v>77121</v>
+        <v>80838</v>
       </c>
     </row>
     <row r="1569">
@@ -20827,10 +20827,10 @@
         </is>
       </c>
       <c r="B1569" s="2" t="n">
-        <v>43770</v>
+        <v>43709</v>
       </c>
       <c r="C1569" t="n">
-        <v>79299</v>
+        <v>76195</v>
       </c>
     </row>
     <row r="1570">
@@ -20840,10 +20840,10 @@
         </is>
       </c>
       <c r="B1570" s="2" t="n">
-        <v>43800</v>
+        <v>43739</v>
       </c>
       <c r="C1570" t="n">
-        <v>89285</v>
+        <v>77121</v>
       </c>
     </row>
     <row r="1571">
@@ -20853,10 +20853,10 @@
         </is>
       </c>
       <c r="B1571" s="2" t="n">
-        <v>43831</v>
+        <v>43770</v>
       </c>
       <c r="C1571" t="n">
-        <v>71688</v>
+        <v>79299</v>
       </c>
     </row>
     <row r="1572">
@@ -20866,10 +20866,10 @@
         </is>
       </c>
       <c r="B1572" s="2" t="n">
-        <v>43862</v>
+        <v>43800</v>
       </c>
       <c r="C1572" t="n">
-        <v>68271</v>
+        <v>89285</v>
       </c>
     </row>
     <row r="1573">
@@ -20879,10 +20879,10 @@
         </is>
       </c>
       <c r="B1573" s="2" t="n">
-        <v>43891</v>
+        <v>43831</v>
       </c>
       <c r="C1573" t="n">
-        <v>60105</v>
+        <v>71688</v>
       </c>
     </row>
     <row r="1574">
@@ -20892,10 +20892,10 @@
         </is>
       </c>
       <c r="B1574" s="2" t="n">
-        <v>43922</v>
+        <v>43862</v>
       </c>
       <c r="C1574" t="n">
-        <v>30109</v>
+        <v>68271</v>
       </c>
     </row>
     <row r="1575">
@@ -20905,10 +20905,10 @@
         </is>
       </c>
       <c r="B1575" s="2" t="n">
-        <v>43952</v>
+        <v>43891</v>
       </c>
       <c r="C1575" t="n">
-        <v>40418</v>
+        <v>60105</v>
       </c>
     </row>
     <row r="1576">
@@ -20918,10 +20918,10 @@
         </is>
       </c>
       <c r="B1576" s="2" t="n">
-        <v>43983</v>
+        <v>43922</v>
       </c>
       <c r="C1576" t="n">
-        <v>58013</v>
+        <v>30109</v>
       </c>
     </row>
     <row r="1577">
@@ -20931,10 +20931,10 @@
         </is>
       </c>
       <c r="B1577" s="2" t="n">
-        <v>44013</v>
+        <v>43952</v>
       </c>
       <c r="C1577" t="n">
-        <v>59335</v>
+        <v>40418</v>
       </c>
     </row>
     <row r="1578">
@@ -20944,10 +20944,10 @@
         </is>
       </c>
       <c r="B1578" s="2" t="n">
-        <v>44044</v>
+        <v>43983</v>
       </c>
       <c r="C1578" t="n">
-        <v>68919</v>
+        <v>58013</v>
       </c>
     </row>
     <row r="1579">
@@ -20957,10 +20957,10 @@
         </is>
       </c>
       <c r="B1579" s="2" t="n">
-        <v>44075</v>
+        <v>44013</v>
       </c>
       <c r="C1579" t="n">
-        <v>77907</v>
+        <v>59335</v>
       </c>
     </row>
     <row r="1580">
@@ -20970,10 +20970,10 @@
         </is>
       </c>
       <c r="B1580" s="2" t="n">
-        <v>44105</v>
+        <v>44044</v>
       </c>
       <c r="C1580" t="n">
-        <v>74115</v>
+        <v>68919</v>
       </c>
     </row>
     <row r="1581">
@@ -20983,10 +20983,10 @@
         </is>
       </c>
       <c r="B1581" s="2" t="n">
-        <v>44136</v>
+        <v>44075</v>
       </c>
       <c r="C1581" t="n">
-        <v>79177</v>
+        <v>77907</v>
       </c>
     </row>
     <row r="1582">
@@ -20996,10 +20996,10 @@
         </is>
       </c>
       <c r="B1582" s="2" t="n">
-        <v>44166</v>
+        <v>44105</v>
       </c>
       <c r="C1582" t="n">
-        <v>104089</v>
+        <v>74115</v>
       </c>
     </row>
     <row r="1583">
@@ -21009,10 +21009,10 @@
         </is>
       </c>
       <c r="B1583" s="2" t="n">
-        <v>44197</v>
+        <v>44136</v>
       </c>
       <c r="C1583" t="n">
-        <v>55208</v>
+        <v>79177</v>
       </c>
     </row>
     <row r="1584">
@@ -21022,10 +21022,10 @@
         </is>
       </c>
       <c r="B1584" s="2" t="n">
-        <v>44228</v>
+        <v>44166</v>
       </c>
       <c r="C1584" t="n">
-        <v>58960</v>
+        <v>104089</v>
       </c>
     </row>
     <row r="1585">
@@ -21035,10 +21035,10 @@
         </is>
       </c>
       <c r="B1585" s="2" t="n">
-        <v>44256</v>
+        <v>44197</v>
       </c>
       <c r="C1585" t="n">
-        <v>74295</v>
+        <v>55208</v>
       </c>
     </row>
     <row r="1586">
@@ -21048,10 +21048,10 @@
         </is>
       </c>
       <c r="B1586" s="2" t="n">
-        <v>44287</v>
+        <v>44228</v>
       </c>
       <c r="C1586" t="n">
-        <v>58132</v>
+        <v>58960</v>
       </c>
     </row>
     <row r="1587">
@@ -21061,10 +21061,10 @@
         </is>
       </c>
       <c r="B1587" s="2" t="n">
-        <v>44317</v>
+        <v>44256</v>
       </c>
       <c r="C1587" t="n">
-        <v>55948</v>
+        <v>74295</v>
       </c>
     </row>
     <row r="1588">
@@ -21074,10 +21074,10 @@
         </is>
       </c>
       <c r="B1588" s="2" t="n">
-        <v>44348</v>
+        <v>44287</v>
       </c>
       <c r="C1588" t="n">
-        <v>61758</v>
+        <v>58132</v>
       </c>
     </row>
     <row r="1589">
@@ -21087,10 +21087,10 @@
         </is>
       </c>
       <c r="B1589" s="2" t="n">
-        <v>44378</v>
+        <v>44317</v>
       </c>
       <c r="C1589" t="n">
-        <v>52442</v>
+        <v>55948</v>
       </c>
     </row>
     <row r="1590">
@@ -21100,10 +21100,10 @@
         </is>
       </c>
       <c r="B1590" s="2" t="n">
-        <v>44409</v>
+        <v>44348</v>
       </c>
       <c r="C1590" t="n">
-        <v>42176</v>
+        <v>61758</v>
       </c>
     </row>
     <row r="1591">
@@ -21113,10 +21113,10 @@
         </is>
       </c>
       <c r="B1591" s="2" t="n">
-        <v>44440</v>
+        <v>44378</v>
       </c>
       <c r="C1591" t="n">
-        <v>56871</v>
+        <v>52442</v>
       </c>
     </row>
     <row r="1592">
@@ -21126,10 +21126,10 @@
         </is>
       </c>
       <c r="B1592" s="2" t="n">
-        <v>44470</v>
+        <v>44409</v>
       </c>
       <c r="C1592" t="n">
-        <v>64462</v>
+        <v>42176</v>
       </c>
     </row>
     <row r="1593">
@@ -21139,10 +21139,10 @@
         </is>
       </c>
       <c r="B1593" s="2" t="n">
-        <v>44501</v>
+        <v>44440</v>
       </c>
       <c r="C1593" t="n">
-        <v>71716</v>
+        <v>56871</v>
       </c>
     </row>
     <row r="1594">
@@ -21152,10 +21152,10 @@
         </is>
       </c>
       <c r="B1594" s="2" t="n">
-        <v>44531</v>
+        <v>44470</v>
       </c>
       <c r="C1594" t="n">
-        <v>86145</v>
+        <v>64462</v>
       </c>
     </row>
     <row r="1595">
@@ -21165,10 +21165,10 @@
         </is>
       </c>
       <c r="B1595" s="2" t="n">
-        <v>44562</v>
+        <v>44501</v>
       </c>
       <c r="C1595" t="n">
-        <v>69455</v>
+        <v>71716</v>
       </c>
     </row>
     <row r="1596">
@@ -21178,10 +21178,10 @@
         </is>
       </c>
       <c r="B1596" s="2" t="n">
-        <v>44593</v>
+        <v>44531</v>
       </c>
       <c r="C1596" t="n">
-        <v>74489</v>
+        <v>86145</v>
       </c>
     </row>
     <row r="1597">
@@ -21191,10 +21191,10 @@
         </is>
       </c>
       <c r="B1597" s="2" t="n">
-        <v>44621</v>
+        <v>44562</v>
       </c>
       <c r="C1597" t="n">
-        <v>87245</v>
+        <v>69455</v>
       </c>
     </row>
     <row r="1598">
@@ -21204,10 +21204,10 @@
         </is>
       </c>
       <c r="B1598" s="2" t="n">
-        <v>44652</v>
+        <v>44593</v>
       </c>
       <c r="C1598" t="n">
-        <v>63427</v>
+        <v>74489</v>
       </c>
     </row>
     <row r="1599">
@@ -21217,10 +21217,10 @@
         </is>
       </c>
       <c r="B1599" s="2" t="n">
-        <v>44682</v>
+        <v>44621</v>
       </c>
       <c r="C1599" t="n">
-        <v>64735</v>
+        <v>87245</v>
       </c>
     </row>
     <row r="1600">
@@ -21230,10 +21230,10 @@
         </is>
       </c>
       <c r="B1600" s="2" t="n">
-        <v>44713</v>
+        <v>44652</v>
       </c>
       <c r="C1600" t="n">
-        <v>67945</v>
+        <v>63427</v>
       </c>
     </row>
     <row r="1601">
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="B1601" s="2" t="n">
-        <v>44743</v>
+        <v>44682</v>
       </c>
       <c r="C1601" t="n">
-        <v>64033</v>
+        <v>64735</v>
       </c>
     </row>
     <row r="1602">
@@ -21256,10 +21256,10 @@
         </is>
       </c>
       <c r="B1602" s="2" t="n">
-        <v>44774</v>
+        <v>44713</v>
       </c>
       <c r="C1602" t="n">
-        <v>68208</v>
+        <v>67945</v>
       </c>
     </row>
     <row r="1603">
@@ -21269,10 +21269,10 @@
         </is>
       </c>
       <c r="B1603" s="2" t="n">
-        <v>44805</v>
+        <v>44743</v>
       </c>
       <c r="C1603" t="n">
-        <v>74150</v>
+        <v>64033</v>
       </c>
     </row>
     <row r="1604">
@@ -21282,10 +21282,10 @@
         </is>
       </c>
       <c r="B1604" s="2" t="n">
-        <v>44835</v>
+        <v>44774</v>
       </c>
       <c r="C1604" t="n">
-        <v>64618</v>
+        <v>68208</v>
       </c>
     </row>
     <row r="1605">
@@ -21295,10 +21295,10 @@
         </is>
       </c>
       <c r="B1605" s="2" t="n">
-        <v>44866</v>
+        <v>44805</v>
       </c>
       <c r="C1605" t="n">
-        <v>68284</v>
+        <v>74150</v>
       </c>
     </row>
     <row r="1606">
@@ -21308,10 +21308,10 @@
         </is>
       </c>
       <c r="B1606" s="2" t="n">
-        <v>44896</v>
+        <v>44835</v>
       </c>
       <c r="C1606" t="n">
-        <v>82799</v>
+        <v>64618</v>
       </c>
     </row>
     <row r="1607">
@@ -21321,10 +21321,10 @@
         </is>
       </c>
       <c r="B1607" s="2" t="n">
-        <v>44927</v>
+        <v>44866</v>
       </c>
       <c r="C1607" t="n">
-        <v>65579</v>
+        <v>68284</v>
       </c>
     </row>
     <row r="1608">
@@ -21334,10 +21334,10 @@
         </is>
       </c>
       <c r="B1608" s="2" t="n">
-        <v>44958</v>
+        <v>44896</v>
       </c>
       <c r="C1608" t="n">
-        <v>71551</v>
+        <v>82799</v>
       </c>
     </row>
     <row r="1609">
@@ -21347,10 +21347,10 @@
         </is>
       </c>
       <c r="B1609" s="2" t="n">
-        <v>44986</v>
+        <v>44927</v>
       </c>
       <c r="C1609" t="n">
-        <v>79943</v>
+        <v>65579</v>
       </c>
     </row>
     <row r="1610">
@@ -21360,10 +21360,10 @@
         </is>
       </c>
       <c r="B1610" s="2" t="n">
-        <v>45017</v>
+        <v>44958</v>
       </c>
       <c r="C1610" t="n">
-        <v>59530</v>
+        <v>71551</v>
       </c>
     </row>
     <row r="1611">
@@ -21373,10 +21373,10 @@
         </is>
       </c>
       <c r="B1611" s="2" t="n">
-        <v>45047</v>
+        <v>44986</v>
       </c>
       <c r="C1611" t="n">
-        <v>65088</v>
+        <v>79943</v>
       </c>
     </row>
     <row r="1612">
@@ -21386,10 +21386,10 @@
         </is>
       </c>
       <c r="B1612" s="2" t="n">
-        <v>45078</v>
+        <v>45017</v>
       </c>
       <c r="C1612" t="n">
-        <v>64440</v>
+        <v>59530</v>
       </c>
     </row>
     <row r="1613">
@@ -21399,10 +21399,10 @@
         </is>
       </c>
       <c r="B1613" s="2" t="n">
-        <v>45108</v>
+        <v>45047</v>
       </c>
       <c r="C1613" t="n">
-        <v>58419</v>
+        <v>65088</v>
       </c>
     </row>
     <row r="1614">
@@ -21412,10 +21412,10 @@
         </is>
       </c>
       <c r="B1614" s="2" t="n">
-        <v>45139</v>
+        <v>45078</v>
       </c>
       <c r="C1614" t="n">
-        <v>60234</v>
+        <v>64440</v>
       </c>
     </row>
     <row r="1615">
@@ -21425,10 +21425,10 @@
         </is>
       </c>
       <c r="B1615" s="2" t="n">
-        <v>45170</v>
+        <v>45108</v>
       </c>
       <c r="C1615" t="n">
-        <v>62086</v>
+        <v>58419</v>
       </c>
     </row>
     <row r="1616">
@@ -21438,10 +21438,10 @@
         </is>
       </c>
       <c r="B1616" s="2" t="n">
-        <v>45200</v>
+        <v>45139</v>
       </c>
       <c r="C1616" t="n">
-        <v>58963</v>
+        <v>60234</v>
       </c>
     </row>
     <row r="1617">
@@ -21451,10 +21451,10 @@
         </is>
       </c>
       <c r="B1617" s="2" t="n">
-        <v>45231</v>
+        <v>45170</v>
       </c>
       <c r="C1617" t="n">
-        <v>61621</v>
+        <v>62086</v>
       </c>
     </row>
     <row r="1618">
@@ -21464,10 +21464,10 @@
         </is>
       </c>
       <c r="B1618" s="2" t="n">
-        <v>45261</v>
+        <v>45200</v>
       </c>
       <c r="C1618" t="n">
-        <v>68326</v>
+        <v>58963</v>
       </c>
     </row>
     <row r="1619">
@@ -21477,10 +21477,10 @@
         </is>
       </c>
       <c r="B1619" s="2" t="n">
-        <v>45292</v>
+        <v>45231</v>
       </c>
       <c r="C1619" t="n">
-        <v>54814</v>
+        <v>61621</v>
       </c>
     </row>
     <row r="1620">
@@ -21490,10 +21490,10 @@
         </is>
       </c>
       <c r="B1620" s="2" t="n">
-        <v>45323</v>
+        <v>45261</v>
       </c>
       <c r="C1620" t="n">
-        <v>52843</v>
+        <v>68326</v>
       </c>
     </row>
     <row r="1621">
@@ -21503,10 +21503,10 @@
         </is>
       </c>
       <c r="B1621" s="2" t="n">
-        <v>45352</v>
+        <v>45292</v>
       </c>
       <c r="C1621" t="n">
-        <v>56099</v>
+        <v>54814</v>
       </c>
     </row>
     <row r="1622">
@@ -21516,10 +21516,10 @@
         </is>
       </c>
       <c r="B1622" s="2" t="n">
-        <v>45383</v>
+        <v>45323</v>
       </c>
       <c r="C1622" t="n">
-        <v>46738</v>
+        <v>52843</v>
       </c>
     </row>
     <row r="1623">
@@ -21529,10 +21529,10 @@
         </is>
       </c>
       <c r="B1623" s="2" t="n">
-        <v>45413</v>
+        <v>45352</v>
       </c>
       <c r="C1623" t="n">
-        <v>49871</v>
+        <v>56099</v>
       </c>
     </row>
     <row r="1624">
@@ -21542,10 +21542,10 @@
         </is>
       </c>
       <c r="B1624" s="2" t="n">
-        <v>45444</v>
+        <v>45383</v>
       </c>
       <c r="C1624" t="n">
-        <v>47662</v>
+        <v>46738</v>
       </c>
     </row>
     <row r="1625">
@@ -21555,10 +21555,10 @@
         </is>
       </c>
       <c r="B1625" s="2" t="n">
-        <v>45474</v>
+        <v>45413</v>
       </c>
       <c r="C1625" t="n">
-        <v>46394</v>
+        <v>49871</v>
       </c>
     </row>
     <row r="1626">
@@ -21568,10 +21568,10 @@
         </is>
       </c>
       <c r="B1626" s="2" t="n">
-        <v>45505</v>
+        <v>45444</v>
       </c>
       <c r="C1626" t="n">
-        <v>45190</v>
+        <v>47662</v>
       </c>
     </row>
     <row r="1627">
@@ -21581,10 +21581,10 @@
         </is>
       </c>
       <c r="B1627" s="2" t="n">
-        <v>45536</v>
+        <v>45474</v>
       </c>
       <c r="C1627" t="n">
-        <v>39048</v>
+        <v>46394</v>
       </c>
     </row>
     <row r="1628">
@@ -21594,10 +21594,10 @@
         </is>
       </c>
       <c r="B1628" s="2" t="n">
-        <v>45566</v>
+        <v>45505</v>
       </c>
       <c r="C1628" t="n">
-        <v>37691</v>
+        <v>45190</v>
       </c>
     </row>
     <row r="1629">
@@ -21607,10 +21607,10 @@
         </is>
       </c>
       <c r="B1629" s="2" t="n">
-        <v>45597</v>
+        <v>45536</v>
       </c>
       <c r="C1629" t="n">
-        <v>42309</v>
+        <v>39048</v>
       </c>
     </row>
     <row r="1630">
@@ -21620,10 +21620,10 @@
         </is>
       </c>
       <c r="B1630" s="2" t="n">
-        <v>45627</v>
+        <v>45566</v>
       </c>
       <c r="C1630" t="n">
-        <v>54016</v>
+        <v>37691</v>
       </c>
     </row>
     <row r="1631">
@@ -21633,10 +21633,10 @@
         </is>
       </c>
       <c r="B1631" s="2" t="n">
-        <v>45658</v>
+        <v>45597</v>
       </c>
       <c r="C1631" t="n">
-        <v>48082</v>
+        <v>42309</v>
       </c>
     </row>
     <row r="1632">
@@ -21646,10 +21646,10 @@
         </is>
       </c>
       <c r="B1632" s="2" t="n">
-        <v>45689</v>
+        <v>45627</v>
       </c>
       <c r="C1632" t="n">
-        <v>49313</v>
+        <v>54016</v>
       </c>
     </row>
     <row r="1633">
@@ -21659,10 +21659,10 @@
         </is>
       </c>
       <c r="B1633" s="2" t="n">
-        <v>45717</v>
+        <v>45658</v>
       </c>
       <c r="C1633" t="n">
-        <v>55798</v>
+        <v>48082</v>
       </c>
     </row>
     <row r="1634">
@@ -21672,10 +21672,10 @@
         </is>
       </c>
       <c r="B1634" s="2" t="n">
-        <v>45748</v>
+        <v>45689</v>
       </c>
       <c r="C1634" t="n">
-        <v>47193</v>
+        <v>49313</v>
       </c>
     </row>
     <row r="1635">
@@ -21685,10 +21685,10 @@
         </is>
       </c>
       <c r="B1635" s="2" t="n">
-        <v>45778</v>
+        <v>45717</v>
       </c>
       <c r="C1635" t="n">
-        <v>52229</v>
+        <v>55798</v>
       </c>
     </row>
     <row r="1636">
@@ -21698,10 +21698,10 @@
         </is>
       </c>
       <c r="B1636" s="2" t="n">
-        <v>45809</v>
+        <v>45748</v>
       </c>
       <c r="C1636" t="n">
-        <v>50079</v>
+        <v>47193</v>
       </c>
     </row>
     <row r="1637">
@@ -21711,10 +21711,10 @@
         </is>
       </c>
       <c r="B1637" s="2" t="n">
-        <v>45839</v>
+        <v>45778</v>
       </c>
       <c r="C1637" t="n">
-        <v>49303</v>
+        <v>52229</v>
       </c>
     </row>
     <row r="1638">
@@ -21724,10 +21724,10 @@
         </is>
       </c>
       <c r="B1638" s="2" t="n">
-        <v>45870</v>
+        <v>45809</v>
       </c>
       <c r="C1638" t="n">
-        <v>47622</v>
+        <v>50079</v>
       </c>
     </row>
     <row r="1639">
@@ -21737,10 +21737,10 @@
         </is>
       </c>
       <c r="B1639" s="2" t="n">
-        <v>45901</v>
+        <v>45839</v>
       </c>
       <c r="C1639" t="n">
-        <v>48350</v>
+        <v>49303</v>
       </c>
     </row>
     <row r="1640">
@@ -21750,10 +21750,10 @@
         </is>
       </c>
       <c r="B1640" s="2" t="n">
-        <v>45931</v>
+        <v>45870</v>
       </c>
       <c r="C1640" t="n">
-        <v>47032</v>
+        <v>47622</v>
       </c>
     </row>
     <row r="1641">
@@ -21763,10 +21763,10 @@
         </is>
       </c>
       <c r="B1641" s="2" t="n">
-        <v>45962</v>
+        <v>45901</v>
       </c>
       <c r="C1641" t="n">
-        <v>51044</v>
+        <v>48350</v>
       </c>
     </row>
     <row r="1642">
@@ -21776,10 +21776,10 @@
         </is>
       </c>
       <c r="B1642" s="2" t="n">
-        <v>45992</v>
+        <v>45931</v>
       </c>
       <c r="C1642" t="n">
-        <v>75121</v>
+        <v>47032</v>
       </c>
     </row>
     <row r="1643">
@@ -21789,10 +21789,10 @@
         </is>
       </c>
       <c r="B1643" s="2" t="n">
-        <v>46023</v>
+        <v>45962</v>
       </c>
       <c r="C1643" t="n">
-        <v>73936</v>
+        <v>51044</v>
       </c>
     </row>
     <row r="1644">
@@ -21802,10 +21802,10 @@
         </is>
       </c>
       <c r="B1644" s="2" t="n">
-        <v>46054</v>
+        <v>45992</v>
       </c>
       <c r="C1644" t="n">
-        <v>48242</v>
+        <v>75121</v>
       </c>
     </row>
     <row r="1645">
@@ -21815,10 +21815,10 @@
         </is>
       </c>
       <c r="B1645" s="2" t="n">
-        <v>46082</v>
+        <v>46023</v>
       </c>
       <c r="C1645" t="n">
-        <v>59865</v>
+        <v>73936</v>
       </c>
     </row>
     <row r="1646">
@@ -21828,10 +21828,10 @@
         </is>
       </c>
       <c r="B1646" s="2" t="n">
-        <v>46113</v>
+        <v>46054</v>
       </c>
       <c r="C1646" t="n">
-        <v>48392</v>
+        <v>48242</v>
       </c>
     </row>
     <row r="1647">
@@ -21841,10 +21841,10 @@
         </is>
       </c>
       <c r="B1647" s="2" t="n">
-        <v>46143</v>
+        <v>46082</v>
       </c>
       <c r="C1647" t="n">
-        <v>57765</v>
+        <v>59865</v>
       </c>
     </row>
     <row r="1648">
@@ -21854,10 +21854,10 @@
         </is>
       </c>
       <c r="B1648" s="2" t="n">
-        <v>46174</v>
+        <v>46113</v>
       </c>
       <c r="C1648" t="n">
-        <v>61244</v>
+        <v>48392</v>
       </c>
     </row>
     <row r="1649">
@@ -21867,10 +21867,10 @@
         </is>
       </c>
       <c r="B1649" s="2" t="n">
-        <v>46204</v>
+        <v>46143</v>
       </c>
       <c r="C1649" t="n">
-        <v>59198</v>
+        <v>57765</v>
       </c>
     </row>
     <row r="1650">
@@ -21880,36 +21880,36 @@
         </is>
       </c>
       <c r="B1650" s="2" t="n">
-        <v>46235</v>
+        <v>46174</v>
       </c>
       <c r="C1650" t="n">
-        <v>59808</v>
+        <v>61244</v>
       </c>
     </row>
     <row r="1651">
       <c r="A1651" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="B1651" s="2" t="n">
-        <v>42401</v>
+        <v>46204</v>
       </c>
       <c r="C1651" t="n">
-        <v>52825</v>
+        <v>59198</v>
       </c>
     </row>
     <row r="1652">
       <c r="A1652" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="B1652" s="2" t="n">
-        <v>42430</v>
+        <v>46235</v>
       </c>
       <c r="C1652" t="n">
-        <v>82948</v>
+        <v>59808</v>
       </c>
     </row>
     <row r="1653">
@@ -21919,10 +21919,10 @@
         </is>
       </c>
       <c r="B1653" s="2" t="n">
-        <v>42461</v>
+        <v>42401</v>
       </c>
       <c r="C1653" t="n">
-        <v>84887</v>
+        <v>52825</v>
       </c>
     </row>
     <row r="1654">
@@ -21932,10 +21932,10 @@
         </is>
       </c>
       <c r="B1654" s="2" t="n">
-        <v>42491</v>
+        <v>42430</v>
       </c>
       <c r="C1654" t="n">
-        <v>93904</v>
+        <v>82948</v>
       </c>
     </row>
     <row r="1655">
@@ -21945,10 +21945,10 @@
         </is>
       </c>
       <c r="B1655" s="2" t="n">
-        <v>42522</v>
+        <v>42461</v>
       </c>
       <c r="C1655" t="n">
-        <v>91540</v>
+        <v>84887</v>
       </c>
     </row>
     <row r="1656">
@@ -21958,10 +21958,10 @@
         </is>
       </c>
       <c r="B1656" s="2" t="n">
-        <v>42552</v>
+        <v>42491</v>
       </c>
       <c r="C1656" t="n">
-        <v>58533</v>
+        <v>93904</v>
       </c>
     </row>
     <row r="1657">
@@ -21971,10 +21971,10 @@
         </is>
       </c>
       <c r="B1657" s="2" t="n">
-        <v>42583</v>
+        <v>42522</v>
       </c>
       <c r="C1657" t="n">
-        <v>71556</v>
+        <v>91540</v>
       </c>
     </row>
     <row r="1658">
@@ -21984,10 +21984,10 @@
         </is>
       </c>
       <c r="B1658" s="2" t="n">
-        <v>42614</v>
+        <v>42552</v>
       </c>
       <c r="C1658" t="n">
-        <v>67593</v>
+        <v>58533</v>
       </c>
     </row>
     <row r="1659">
@@ -21997,10 +21997,10 @@
         </is>
       </c>
       <c r="B1659" s="2" t="n">
-        <v>42644</v>
+        <v>42583</v>
       </c>
       <c r="C1659" t="n">
-        <v>83000</v>
+        <v>71556</v>
       </c>
     </row>
     <row r="1660">
@@ -22010,10 +22010,10 @@
         </is>
       </c>
       <c r="B1660" s="2" t="n">
-        <v>42675</v>
+        <v>42614</v>
       </c>
       <c r="C1660" t="n">
-        <v>122309</v>
+        <v>67593</v>
       </c>
     </row>
     <row r="1661">
@@ -22023,10 +22023,10 @@
         </is>
       </c>
       <c r="B1661" s="2" t="n">
-        <v>42705</v>
+        <v>42644</v>
       </c>
       <c r="C1661" t="n">
-        <v>141912</v>
+        <v>83000</v>
       </c>
     </row>
     <row r="1662">
@@ -22036,10 +22036,10 @@
         </is>
       </c>
       <c r="B1662" s="2" t="n">
-        <v>42736</v>
+        <v>42675</v>
       </c>
       <c r="C1662" t="n">
-        <v>35323</v>
+        <v>122309</v>
       </c>
     </row>
     <row r="1663">
@@ -22049,10 +22049,10 @@
         </is>
       </c>
       <c r="B1663" s="2" t="n">
-        <v>42767</v>
+        <v>42705</v>
       </c>
       <c r="C1663" t="n">
-        <v>46965</v>
+        <v>141912</v>
       </c>
     </row>
     <row r="1664">
@@ -22062,10 +22062,10 @@
         </is>
       </c>
       <c r="B1664" s="2" t="n">
-        <v>42795</v>
+        <v>42736</v>
       </c>
       <c r="C1664" t="n">
-        <v>73802</v>
+        <v>35323</v>
       </c>
     </row>
     <row r="1665">
@@ -22075,10 +22075,10 @@
         </is>
       </c>
       <c r="B1665" s="2" t="n">
-        <v>42826</v>
+        <v>42767</v>
       </c>
       <c r="C1665" t="n">
-        <v>75988</v>
+        <v>46965</v>
       </c>
     </row>
     <row r="1666">
@@ -22088,10 +22088,10 @@
         </is>
       </c>
       <c r="B1666" s="2" t="n">
-        <v>42856</v>
+        <v>42795</v>
       </c>
       <c r="C1666" t="n">
-        <v>85422</v>
+        <v>73802</v>
       </c>
     </row>
     <row r="1667">
@@ -22101,10 +22101,10 @@
         </is>
       </c>
       <c r="B1667" s="2" t="n">
-        <v>42887</v>
+        <v>42826</v>
       </c>
       <c r="C1667" t="n">
-        <v>83658</v>
+        <v>75988</v>
       </c>
     </row>
     <row r="1668">
@@ -22114,10 +22114,10 @@
         </is>
       </c>
       <c r="B1668" s="2" t="n">
-        <v>42917</v>
+        <v>42856</v>
       </c>
       <c r="C1668" t="n">
-        <v>82297</v>
+        <v>85422</v>
       </c>
     </row>
     <row r="1669">
@@ -22127,10 +22127,10 @@
         </is>
       </c>
       <c r="B1669" s="2" t="n">
-        <v>42948</v>
+        <v>42887</v>
       </c>
       <c r="C1669" t="n">
-        <v>72536</v>
+        <v>83658</v>
       </c>
     </row>
     <row r="1670">
@@ -22140,10 +22140,10 @@
         </is>
       </c>
       <c r="B1670" s="2" t="n">
-        <v>42979</v>
+        <v>42917</v>
       </c>
       <c r="C1670" t="n">
-        <v>71352</v>
+        <v>82297</v>
       </c>
     </row>
     <row r="1671">
@@ -22153,10 +22153,10 @@
         </is>
       </c>
       <c r="B1671" s="2" t="n">
-        <v>43009</v>
+        <v>42948</v>
       </c>
       <c r="C1671" t="n">
-        <v>91752</v>
+        <v>72536</v>
       </c>
     </row>
     <row r="1672">
@@ -22166,10 +22166,10 @@
         </is>
       </c>
       <c r="B1672" s="2" t="n">
-        <v>43040</v>
+        <v>42979</v>
       </c>
       <c r="C1672" t="n">
-        <v>100859</v>
+        <v>71352</v>
       </c>
     </row>
     <row r="1673">
@@ -22179,10 +22179,10 @@
         </is>
       </c>
       <c r="B1673" s="2" t="n">
-        <v>43070</v>
+        <v>43009</v>
       </c>
       <c r="C1673" t="n">
-        <v>136240</v>
+        <v>91752</v>
       </c>
     </row>
     <row r="1674">
@@ -22192,10 +22192,10 @@
         </is>
       </c>
       <c r="B1674" s="2" t="n">
-        <v>43101</v>
+        <v>43040</v>
       </c>
       <c r="C1674" t="n">
-        <v>35076</v>
+        <v>100859</v>
       </c>
     </row>
     <row r="1675">
@@ -22205,10 +22205,10 @@
         </is>
       </c>
       <c r="B1675" s="2" t="n">
-        <v>43132</v>
+        <v>43070</v>
       </c>
       <c r="C1675" t="n">
-        <v>47009</v>
+        <v>136240</v>
       </c>
     </row>
     <row r="1676">
@@ -22218,10 +22218,10 @@
         </is>
       </c>
       <c r="B1676" s="2" t="n">
-        <v>43160</v>
+        <v>43101</v>
       </c>
       <c r="C1676" t="n">
-        <v>76345</v>
+        <v>35076</v>
       </c>
     </row>
     <row r="1677">
@@ -22231,10 +22231,10 @@
         </is>
       </c>
       <c r="B1677" s="2" t="n">
-        <v>43191</v>
+        <v>43132</v>
       </c>
       <c r="C1677" t="n">
-        <v>71126</v>
+        <v>47009</v>
       </c>
     </row>
     <row r="1678">
@@ -22244,10 +22244,10 @@
         </is>
       </c>
       <c r="B1678" s="2" t="n">
-        <v>43221</v>
+        <v>43160</v>
       </c>
       <c r="C1678" t="n">
-        <v>72755</v>
+        <v>76345</v>
       </c>
     </row>
     <row r="1679">
@@ -22257,10 +22257,10 @@
         </is>
       </c>
       <c r="B1679" s="2" t="n">
-        <v>43252</v>
+        <v>43191</v>
       </c>
       <c r="C1679" t="n">
-        <v>51037</v>
+        <v>71126</v>
       </c>
     </row>
     <row r="1680">
@@ -22270,10 +22270,10 @@
         </is>
       </c>
       <c r="B1680" s="2" t="n">
-        <v>43282</v>
+        <v>43221</v>
       </c>
       <c r="C1680" t="n">
-        <v>52734</v>
+        <v>72755</v>
       </c>
     </row>
     <row r="1681">
@@ -22283,10 +22283,10 @@
         </is>
       </c>
       <c r="B1681" s="2" t="n">
-        <v>43313</v>
+        <v>43252</v>
       </c>
       <c r="C1681" t="n">
-        <v>34346</v>
+        <v>51037</v>
       </c>
     </row>
     <row r="1682">
@@ -22296,10 +22296,10 @@
         </is>
       </c>
       <c r="B1682" s="2" t="n">
-        <v>43344</v>
+        <v>43282</v>
       </c>
       <c r="C1682" t="n">
-        <v>23028</v>
+        <v>52734</v>
       </c>
     </row>
     <row r="1683">
@@ -22309,10 +22309,10 @@
         </is>
       </c>
       <c r="B1683" s="2" t="n">
-        <v>43374</v>
+        <v>43313</v>
       </c>
       <c r="C1683" t="n">
-        <v>21571</v>
+        <v>34346</v>
       </c>
     </row>
     <row r="1684">
@@ -22322,10 +22322,10 @@
         </is>
       </c>
       <c r="B1684" s="2" t="n">
-        <v>43405</v>
+        <v>43344</v>
       </c>
       <c r="C1684" t="n">
-        <v>58204</v>
+        <v>23028</v>
       </c>
     </row>
     <row r="1685">
@@ -22335,10 +22335,10 @@
         </is>
       </c>
       <c r="B1685" s="2" t="n">
-        <v>43435</v>
+        <v>43374</v>
       </c>
       <c r="C1685" t="n">
-        <v>77706</v>
+        <v>21571</v>
       </c>
     </row>
     <row r="1686">
@@ -22348,10 +22348,10 @@
         </is>
       </c>
       <c r="B1686" s="2" t="n">
-        <v>43466</v>
+        <v>43405</v>
       </c>
       <c r="C1686" t="n">
-        <v>14373</v>
+        <v>58204</v>
       </c>
     </row>
     <row r="1687">
@@ -22361,10 +22361,10 @@
         </is>
       </c>
       <c r="B1687" s="2" t="n">
-        <v>43497</v>
+        <v>43435</v>
       </c>
       <c r="C1687" t="n">
-        <v>24875</v>
+        <v>77706</v>
       </c>
     </row>
     <row r="1688">
@@ -22374,10 +22374,10 @@
         </is>
       </c>
       <c r="B1688" s="2" t="n">
-        <v>43525</v>
+        <v>43466</v>
       </c>
       <c r="C1688" t="n">
-        <v>49221</v>
+        <v>14373</v>
       </c>
     </row>
     <row r="1689">
@@ -22387,10 +22387,10 @@
         </is>
       </c>
       <c r="B1689" s="2" t="n">
-        <v>43556</v>
+        <v>43497</v>
       </c>
       <c r="C1689" t="n">
-        <v>30971</v>
+        <v>24875</v>
       </c>
     </row>
     <row r="1690">
@@ -22400,10 +22400,10 @@
         </is>
       </c>
       <c r="B1690" s="2" t="n">
-        <v>43586</v>
+        <v>43525</v>
       </c>
       <c r="C1690" t="n">
-        <v>33016</v>
+        <v>49221</v>
       </c>
     </row>
     <row r="1691">
@@ -22413,10 +22413,10 @@
         </is>
       </c>
       <c r="B1691" s="2" t="n">
-        <v>43617</v>
+        <v>43556</v>
       </c>
       <c r="C1691" t="n">
-        <v>42688</v>
+        <v>30971</v>
       </c>
     </row>
     <row r="1692">
@@ -22426,10 +22426,10 @@
         </is>
       </c>
       <c r="B1692" s="2" t="n">
-        <v>43647</v>
+        <v>43586</v>
       </c>
       <c r="C1692" t="n">
-        <v>17927</v>
+        <v>33016</v>
       </c>
     </row>
     <row r="1693">
@@ -22439,10 +22439,10 @@
         </is>
       </c>
       <c r="B1693" s="2" t="n">
-        <v>43678</v>
+        <v>43617</v>
       </c>
       <c r="C1693" t="n">
-        <v>26246</v>
+        <v>42688</v>
       </c>
     </row>
     <row r="1694">
@@ -22452,10 +22452,10 @@
         </is>
       </c>
       <c r="B1694" s="2" t="n">
-        <v>43709</v>
+        <v>43647</v>
       </c>
       <c r="C1694" t="n">
-        <v>41992</v>
+        <v>17927</v>
       </c>
     </row>
     <row r="1695">
@@ -22465,10 +22465,10 @@
         </is>
       </c>
       <c r="B1695" s="2" t="n">
-        <v>43739</v>
+        <v>43678</v>
       </c>
       <c r="C1695" t="n">
-        <v>49075</v>
+        <v>26246</v>
       </c>
     </row>
     <row r="1696">
@@ -22478,10 +22478,10 @@
         </is>
       </c>
       <c r="B1696" s="2" t="n">
-        <v>43770</v>
+        <v>43709</v>
       </c>
       <c r="C1696" t="n">
-        <v>58176</v>
+        <v>41992</v>
       </c>
     </row>
     <row r="1697">
@@ -22491,10 +22491,10 @@
         </is>
       </c>
       <c r="B1697" s="2" t="n">
-        <v>43800</v>
+        <v>43739</v>
       </c>
       <c r="C1697" t="n">
-        <v>90500</v>
+        <v>49075</v>
       </c>
     </row>
     <row r="1698">
@@ -22504,10 +22504,10 @@
         </is>
       </c>
       <c r="B1698" s="2" t="n">
-        <v>43831</v>
+        <v>43770</v>
       </c>
       <c r="C1698" t="n">
-        <v>27273</v>
+        <v>58176</v>
       </c>
     </row>
     <row r="1699">
@@ -22517,10 +22517,10 @@
         </is>
       </c>
       <c r="B1699" s="2" t="n">
-        <v>43862</v>
+        <v>43800</v>
       </c>
       <c r="C1699" t="n">
-        <v>47122</v>
+        <v>90500</v>
       </c>
     </row>
     <row r="1700">
@@ -22530,10 +22530,10 @@
         </is>
       </c>
       <c r="B1700" s="2" t="n">
-        <v>43891</v>
+        <v>43831</v>
       </c>
       <c r="C1700" t="n">
-        <v>50008</v>
+        <v>27273</v>
       </c>
     </row>
     <row r="1701">
@@ -22543,10 +22543,10 @@
         </is>
       </c>
       <c r="B1701" s="2" t="n">
-        <v>43922</v>
+        <v>43862</v>
       </c>
       <c r="C1701" t="n">
-        <v>26457</v>
+        <v>47122</v>
       </c>
     </row>
     <row r="1702">
@@ -22556,10 +22556,10 @@
         </is>
       </c>
       <c r="B1702" s="2" t="n">
-        <v>43952</v>
+        <v>43891</v>
       </c>
       <c r="C1702" t="n">
-        <v>32235</v>
+        <v>50008</v>
       </c>
     </row>
     <row r="1703">
@@ -22569,10 +22569,10 @@
         </is>
       </c>
       <c r="B1703" s="2" t="n">
-        <v>43983</v>
+        <v>43922</v>
       </c>
       <c r="C1703" t="n">
-        <v>70973</v>
+        <v>26457</v>
       </c>
     </row>
     <row r="1704">
@@ -22582,10 +22582,10 @@
         </is>
       </c>
       <c r="B1704" s="2" t="n">
-        <v>44013</v>
+        <v>43952</v>
       </c>
       <c r="C1704" t="n">
-        <v>87401</v>
+        <v>32235</v>
       </c>
     </row>
     <row r="1705">
@@ -22595,10 +22595,10 @@
         </is>
       </c>
       <c r="B1705" s="2" t="n">
-        <v>44044</v>
+        <v>43983</v>
       </c>
       <c r="C1705" t="n">
-        <v>61533</v>
+        <v>70973</v>
       </c>
     </row>
     <row r="1706">
@@ -22608,10 +22608,10 @@
         </is>
       </c>
       <c r="B1706" s="2" t="n">
-        <v>44075</v>
+        <v>44013</v>
       </c>
       <c r="C1706" t="n">
-        <v>90619</v>
+        <v>87401</v>
       </c>
     </row>
     <row r="1707">
@@ -22621,10 +22621,10 @@
         </is>
       </c>
       <c r="B1707" s="2" t="n">
-        <v>44105</v>
+        <v>44044</v>
       </c>
       <c r="C1707" t="n">
-        <v>94733</v>
+        <v>61533</v>
       </c>
     </row>
     <row r="1708">
@@ -22634,10 +22634,10 @@
         </is>
       </c>
       <c r="B1708" s="2" t="n">
-        <v>44136</v>
+        <v>44075</v>
       </c>
       <c r="C1708" t="n">
-        <v>80141</v>
+        <v>90619</v>
       </c>
     </row>
     <row r="1709">
@@ -22647,10 +22647,10 @@
         </is>
       </c>
       <c r="B1709" s="2" t="n">
-        <v>44166</v>
+        <v>44105</v>
       </c>
       <c r="C1709" t="n">
-        <v>104293</v>
+        <v>94733</v>
       </c>
     </row>
     <row r="1710">
@@ -22660,10 +22660,10 @@
         </is>
       </c>
       <c r="B1710" s="2" t="n">
-        <v>44197</v>
+        <v>44136</v>
       </c>
       <c r="C1710" t="n">
-        <v>43728</v>
+        <v>80141</v>
       </c>
     </row>
     <row r="1711">
@@ -22673,10 +22673,10 @@
         </is>
       </c>
       <c r="B1711" s="2" t="n">
-        <v>44228</v>
+        <v>44166</v>
       </c>
       <c r="C1711" t="n">
-        <v>58504</v>
+        <v>104293</v>
       </c>
     </row>
     <row r="1712">
@@ -22686,10 +22686,10 @@
         </is>
       </c>
       <c r="B1712" s="2" t="n">
-        <v>44256</v>
+        <v>44197</v>
       </c>
       <c r="C1712" t="n">
-        <v>96428</v>
+        <v>43728</v>
       </c>
     </row>
     <row r="1713">
@@ -22699,10 +22699,10 @@
         </is>
       </c>
       <c r="B1713" s="2" t="n">
-        <v>44287</v>
+        <v>44228</v>
       </c>
       <c r="C1713" t="n">
-        <v>61488</v>
+        <v>58504</v>
       </c>
     </row>
     <row r="1714">
@@ -22712,10 +22712,10 @@
         </is>
       </c>
       <c r="B1714" s="2" t="n">
-        <v>44317</v>
+        <v>44256</v>
       </c>
       <c r="C1714" t="n">
-        <v>54734</v>
+        <v>96428</v>
       </c>
     </row>
     <row r="1715">
@@ -22725,10 +22725,10 @@
         </is>
       </c>
       <c r="B1715" s="2" t="n">
-        <v>44348</v>
+        <v>44287</v>
       </c>
       <c r="C1715" t="n">
-        <v>79819</v>
+        <v>61488</v>
       </c>
     </row>
     <row r="1716">
@@ -22738,10 +22738,10 @@
         </is>
       </c>
       <c r="B1716" s="2" t="n">
-        <v>44378</v>
+        <v>44317</v>
       </c>
       <c r="C1716" t="n">
-        <v>47849</v>
+        <v>54734</v>
       </c>
     </row>
     <row r="1717">
@@ -22751,10 +22751,10 @@
         </is>
       </c>
       <c r="B1717" s="2" t="n">
-        <v>44409</v>
+        <v>44348</v>
       </c>
       <c r="C1717" t="n">
-        <v>58454</v>
+        <v>79819</v>
       </c>
     </row>
     <row r="1718">
@@ -22764,10 +22764,10 @@
         </is>
       </c>
       <c r="B1718" s="2" t="n">
-        <v>44440</v>
+        <v>44378</v>
       </c>
       <c r="C1718" t="n">
-        <v>57141</v>
+        <v>47849</v>
       </c>
     </row>
     <row r="1719">
@@ -22777,10 +22777,10 @@
         </is>
       </c>
       <c r="B1719" s="2" t="n">
-        <v>44470</v>
+        <v>44409</v>
       </c>
       <c r="C1719" t="n">
-        <v>56746</v>
+        <v>58454</v>
       </c>
     </row>
     <row r="1720">
@@ -22790,10 +22790,10 @@
         </is>
       </c>
       <c r="B1720" s="2" t="n">
-        <v>44501</v>
+        <v>44440</v>
       </c>
       <c r="C1720" t="n">
-        <v>60216</v>
+        <v>57141</v>
       </c>
     </row>
     <row r="1721">
@@ -22803,10 +22803,10 @@
         </is>
       </c>
       <c r="B1721" s="2" t="n">
-        <v>44531</v>
+        <v>44470</v>
       </c>
       <c r="C1721" t="n">
-        <v>62243</v>
+        <v>56746</v>
       </c>
     </row>
     <row r="1722">
@@ -22816,10 +22816,10 @@
         </is>
       </c>
       <c r="B1722" s="2" t="n">
-        <v>44562</v>
+        <v>44501</v>
       </c>
       <c r="C1722" t="n">
-        <v>38131</v>
+        <v>60216</v>
       </c>
     </row>
     <row r="1723">
@@ -22829,10 +22829,10 @@
         </is>
       </c>
       <c r="B1723" s="2" t="n">
-        <v>44593</v>
+        <v>44531</v>
       </c>
       <c r="C1723" t="n">
-        <v>49652</v>
+        <v>62243</v>
       </c>
     </row>
     <row r="1724">
@@ -22842,10 +22842,10 @@
         </is>
       </c>
       <c r="B1724" s="2" t="n">
-        <v>44621</v>
+        <v>44562</v>
       </c>
       <c r="C1724" t="n">
-        <v>64267</v>
+        <v>38131</v>
       </c>
     </row>
     <row r="1725">
@@ -22855,10 +22855,10 @@
         </is>
       </c>
       <c r="B1725" s="2" t="n">
-        <v>44652</v>
+        <v>44593</v>
       </c>
       <c r="C1725" t="n">
-        <v>60035</v>
+        <v>49652</v>
       </c>
     </row>
     <row r="1726">
@@ -22868,10 +22868,10 @@
         </is>
       </c>
       <c r="B1726" s="2" t="n">
-        <v>44682</v>
+        <v>44621</v>
       </c>
       <c r="C1726" t="n">
-        <v>65167</v>
+        <v>64267</v>
       </c>
     </row>
     <row r="1727">
@@ -22881,10 +22881,10 @@
         </is>
       </c>
       <c r="B1727" s="2" t="n">
-        <v>44713</v>
+        <v>44652</v>
       </c>
       <c r="C1727" t="n">
-        <v>80652</v>
+        <v>60035</v>
       </c>
     </row>
     <row r="1728">
@@ -22894,10 +22894,10 @@
         </is>
       </c>
       <c r="B1728" s="2" t="n">
-        <v>44743</v>
+        <v>44682</v>
       </c>
       <c r="C1728" t="n">
-        <v>52206</v>
+        <v>65167</v>
       </c>
     </row>
     <row r="1729">
@@ -22907,10 +22907,10 @@
         </is>
       </c>
       <c r="B1729" s="2" t="n">
-        <v>44774</v>
+        <v>44713</v>
       </c>
       <c r="C1729" t="n">
-        <v>48336</v>
+        <v>80652</v>
       </c>
     </row>
     <row r="1730">
@@ -22920,10 +22920,10 @@
         </is>
       </c>
       <c r="B1730" s="2" t="n">
-        <v>44805</v>
+        <v>44743</v>
       </c>
       <c r="C1730" t="n">
-        <v>62084</v>
+        <v>52206</v>
       </c>
     </row>
     <row r="1731">
@@ -22933,10 +22933,10 @@
         </is>
       </c>
       <c r="B1731" s="2" t="n">
-        <v>44835</v>
+        <v>44774</v>
       </c>
       <c r="C1731" t="n">
-        <v>65222</v>
+        <v>48336</v>
       </c>
     </row>
     <row r="1732">
@@ -22946,10 +22946,10 @@
         </is>
       </c>
       <c r="B1732" s="2" t="n">
-        <v>44866</v>
+        <v>44805</v>
       </c>
       <c r="C1732" t="n">
-        <v>82311</v>
+        <v>62084</v>
       </c>
     </row>
     <row r="1733">
@@ -22959,10 +22959,10 @@
         </is>
       </c>
       <c r="B1733" s="2" t="n">
-        <v>44896</v>
+        <v>44835</v>
       </c>
       <c r="C1733" t="n">
-        <v>115220</v>
+        <v>65222</v>
       </c>
     </row>
     <row r="1734">
@@ -22972,10 +22972,10 @@
         </is>
       </c>
       <c r="B1734" s="2" t="n">
-        <v>44927</v>
+        <v>44866</v>
       </c>
       <c r="C1734" t="n">
-        <v>50894</v>
+        <v>82311</v>
       </c>
     </row>
     <row r="1735">
@@ -22985,10 +22985,10 @@
         </is>
       </c>
       <c r="B1735" s="2" t="n">
-        <v>44958</v>
+        <v>44896</v>
       </c>
       <c r="C1735" t="n">
-        <v>81148</v>
+        <v>115220</v>
       </c>
     </row>
     <row r="1736">
@@ -22998,10 +22998,10 @@
         </is>
       </c>
       <c r="B1736" s="2" t="n">
-        <v>44986</v>
+        <v>44927</v>
       </c>
       <c r="C1736" t="n">
-        <v>103929</v>
+        <v>50894</v>
       </c>
     </row>
     <row r="1737">
@@ -23011,10 +23011,10 @@
         </is>
       </c>
       <c r="B1737" s="2" t="n">
-        <v>45017</v>
+        <v>44958</v>
       </c>
       <c r="C1737" t="n">
-        <v>97679</v>
+        <v>81148</v>
       </c>
     </row>
     <row r="1738">
@@ -23024,10 +23024,10 @@
         </is>
       </c>
       <c r="B1738" s="2" t="n">
-        <v>45047</v>
+        <v>44986</v>
       </c>
       <c r="C1738" t="n">
-        <v>111356</v>
+        <v>103929</v>
       </c>
     </row>
     <row r="1739">
@@ -23037,10 +23037,10 @@
         </is>
       </c>
       <c r="B1739" s="2" t="n">
-        <v>45078</v>
+        <v>45017</v>
       </c>
       <c r="C1739" t="n">
-        <v>110861</v>
+        <v>97679</v>
       </c>
     </row>
     <row r="1740">
@@ -23050,10 +23050,10 @@
         </is>
       </c>
       <c r="B1740" s="2" t="n">
-        <v>45108</v>
+        <v>45047</v>
       </c>
       <c r="C1740" t="n">
-        <v>112459</v>
+        <v>111356</v>
       </c>
     </row>
     <row r="1741">
@@ -23063,10 +23063,10 @@
         </is>
       </c>
       <c r="B1741" s="2" t="n">
-        <v>45139</v>
+        <v>45078</v>
       </c>
       <c r="C1741" t="n">
-        <v>86454</v>
+        <v>110861</v>
       </c>
     </row>
     <row r="1742">
@@ -23076,10 +23076,10 @@
         </is>
       </c>
       <c r="B1742" s="2" t="n">
-        <v>45170</v>
+        <v>45108</v>
       </c>
       <c r="C1742" t="n">
-        <v>96793</v>
+        <v>112459</v>
       </c>
     </row>
     <row r="1743">
@@ -23089,10 +23089,10 @@
         </is>
       </c>
       <c r="B1743" s="2" t="n">
-        <v>45200</v>
+        <v>45139</v>
       </c>
       <c r="C1743" t="n">
-        <v>101367</v>
+        <v>86454</v>
       </c>
     </row>
     <row r="1744">
@@ -23102,10 +23102,10 @@
         </is>
       </c>
       <c r="B1744" s="2" t="n">
-        <v>45231</v>
+        <v>45170</v>
       </c>
       <c r="C1744" t="n">
-        <v>115040</v>
+        <v>96793</v>
       </c>
     </row>
     <row r="1745">
@@ -23115,10 +23115,10 @@
         </is>
       </c>
       <c r="B1745" s="2" t="n">
-        <v>45261</v>
+        <v>45200</v>
       </c>
       <c r="C1745" t="n">
-        <v>158653</v>
+        <v>101367</v>
       </c>
     </row>
     <row r="1746">
@@ -23128,10 +23128,10 @@
         </is>
       </c>
       <c r="B1746" s="2" t="n">
-        <v>45292</v>
+        <v>45231</v>
       </c>
       <c r="C1746" t="n">
-        <v>79701</v>
+        <v>115040</v>
       </c>
     </row>
     <row r="1747">
@@ -23141,10 +23141,10 @@
         </is>
       </c>
       <c r="B1747" s="2" t="n">
-        <v>45323</v>
+        <v>45261</v>
       </c>
       <c r="C1747" t="n">
-        <v>105990</v>
+        <v>158653</v>
       </c>
     </row>
     <row r="1748">
@@ -23154,10 +23154,10 @@
         </is>
       </c>
       <c r="B1748" s="2" t="n">
-        <v>45352</v>
+        <v>45292</v>
       </c>
       <c r="C1748" t="n">
-        <v>109828</v>
+        <v>79701</v>
       </c>
     </row>
     <row r="1749">
@@ -23167,10 +23167,10 @@
         </is>
       </c>
       <c r="B1749" s="2" t="n">
-        <v>45383</v>
+        <v>45323</v>
       </c>
       <c r="C1749" t="n">
-        <v>75919</v>
+        <v>105990</v>
       </c>
     </row>
     <row r="1750">
@@ -23180,10 +23180,10 @@
         </is>
       </c>
       <c r="B1750" s="2" t="n">
-        <v>45413</v>
+        <v>45352</v>
       </c>
       <c r="C1750" t="n">
-        <v>100305</v>
+        <v>109828</v>
       </c>
     </row>
     <row r="1751">
@@ -23193,10 +23193,10 @@
         </is>
       </c>
       <c r="B1751" s="2" t="n">
-        <v>45444</v>
+        <v>45383</v>
       </c>
       <c r="C1751" t="n">
-        <v>106238</v>
+        <v>75919</v>
       </c>
     </row>
     <row r="1752">
@@ -23206,10 +23206,10 @@
         </is>
       </c>
       <c r="B1752" s="2" t="n">
-        <v>45474</v>
+        <v>45413</v>
       </c>
       <c r="C1752" t="n">
-        <v>94037</v>
+        <v>100305</v>
       </c>
     </row>
     <row r="1753">
@@ -23219,10 +23219,10 @@
         </is>
       </c>
       <c r="B1753" s="2" t="n">
-        <v>45505</v>
+        <v>45444</v>
       </c>
       <c r="C1753" t="n">
-        <v>90134</v>
+        <v>106238</v>
       </c>
     </row>
     <row r="1754">
@@ -23232,10 +23232,10 @@
         </is>
       </c>
       <c r="B1754" s="2" t="n">
-        <v>45536</v>
+        <v>45474</v>
       </c>
       <c r="C1754" t="n">
-        <v>85540</v>
+        <v>94037</v>
       </c>
     </row>
     <row r="1755">
@@ -23245,10 +23245,10 @@
         </is>
       </c>
       <c r="B1755" s="2" t="n">
-        <v>45566</v>
+        <v>45505</v>
       </c>
       <c r="C1755" t="n">
-        <v>97274</v>
+        <v>90134</v>
       </c>
     </row>
     <row r="1756">
@@ -23258,10 +23258,10 @@
         </is>
       </c>
       <c r="B1756" s="2" t="n">
-        <v>45597</v>
+        <v>45536</v>
       </c>
       <c r="C1756" t="n">
-        <v>121094</v>
+        <v>85540</v>
       </c>
     </row>
     <row r="1757">
@@ -23271,10 +23271,10 @@
         </is>
       </c>
       <c r="B1757" s="2" t="n">
-        <v>45627</v>
+        <v>45566</v>
       </c>
       <c r="C1757" t="n">
-        <v>170249</v>
+        <v>97274</v>
       </c>
     </row>
     <row r="1758">
@@ -23284,10 +23284,10 @@
         </is>
       </c>
       <c r="B1758" s="2" t="n">
-        <v>45658</v>
+        <v>45597</v>
       </c>
       <c r="C1758" t="n">
-        <v>68654</v>
+        <v>121094</v>
       </c>
     </row>
     <row r="1759">
@@ -23297,10 +23297,10 @@
         </is>
       </c>
       <c r="B1759" s="2" t="n">
-        <v>45689</v>
+        <v>45627</v>
       </c>
       <c r="C1759" t="n">
-        <v>90730</v>
+        <v>170249</v>
       </c>
     </row>
     <row r="1760">
@@ -23310,10 +23310,10 @@
         </is>
       </c>
       <c r="B1760" s="2" t="n">
-        <v>45717</v>
+        <v>45658</v>
       </c>
       <c r="C1760" t="n">
-        <v>116900</v>
+        <v>68654</v>
       </c>
     </row>
     <row r="1761">
@@ -23323,10 +23323,10 @@
         </is>
       </c>
       <c r="B1761" s="2" t="n">
-        <v>45748</v>
+        <v>45689</v>
       </c>
       <c r="C1761" t="n">
-        <v>105352</v>
+        <v>90730</v>
       </c>
     </row>
     <row r="1762">
@@ -23336,10 +23336,10 @@
         </is>
       </c>
       <c r="B1762" s="2" t="n">
-        <v>45778</v>
+        <v>45717</v>
       </c>
       <c r="C1762" t="n">
-        <v>107730</v>
+        <v>116900</v>
       </c>
     </row>
     <row r="1763">
@@ -23349,10 +23349,10 @@
         </is>
       </c>
       <c r="B1763" s="2" t="n">
-        <v>45809</v>
+        <v>45748</v>
       </c>
       <c r="C1763" t="n">
-        <v>118611</v>
+        <v>105352</v>
       </c>
     </row>
     <row r="1764">
@@ -23362,10 +23362,10 @@
         </is>
       </c>
       <c r="B1764" s="2" t="n">
-        <v>45839</v>
+        <v>45778</v>
       </c>
       <c r="C1764" t="n">
-        <v>107718</v>
+        <v>107730</v>
       </c>
     </row>
     <row r="1765">
@@ -23375,10 +23375,10 @@
         </is>
       </c>
       <c r="B1765" s="2" t="n">
-        <v>45870</v>
+        <v>45809</v>
       </c>
       <c r="C1765" t="n">
-        <v>101650</v>
+        <v>118611</v>
       </c>
     </row>
     <row r="1766">
@@ -23388,10 +23388,10 @@
         </is>
       </c>
       <c r="B1766" s="2" t="n">
-        <v>45901</v>
+        <v>45839</v>
       </c>
       <c r="C1766" t="n">
-        <v>110302</v>
+        <v>107718</v>
       </c>
     </row>
     <row r="1767">
@@ -23401,10 +23401,10 @@
         </is>
       </c>
       <c r="B1767" s="2" t="n">
-        <v>45931</v>
+        <v>45870</v>
       </c>
       <c r="C1767" t="n">
-        <v>116149</v>
+        <v>101650</v>
       </c>
     </row>
     <row r="1768">
@@ -23414,10 +23414,10 @@
         </is>
       </c>
       <c r="B1768" s="2" t="n">
-        <v>45962</v>
+        <v>45901</v>
       </c>
       <c r="C1768" t="n">
-        <v>132984</v>
+        <v>110302</v>
       </c>
     </row>
     <row r="1769">
@@ -23427,10 +23427,10 @@
         </is>
       </c>
       <c r="B1769" s="2" t="n">
-        <v>45992</v>
+        <v>45931</v>
       </c>
       <c r="C1769" t="n">
-        <v>191620</v>
+        <v>116149</v>
       </c>
     </row>
     <row r="1770">
@@ -23440,10 +23440,10 @@
         </is>
       </c>
       <c r="B1770" s="2" t="n">
-        <v>46023</v>
+        <v>45962</v>
       </c>
       <c r="C1770" t="n">
-        <v>75362</v>
+        <v>132984</v>
       </c>
     </row>
     <row r="1771">
@@ -23453,10 +23453,10 @@
         </is>
       </c>
       <c r="B1771" s="2" t="n">
-        <v>46054</v>
+        <v>45992</v>
       </c>
       <c r="C1771" t="n">
-        <v>88039</v>
+        <v>191620</v>
       </c>
     </row>
     <row r="1772">
@@ -23466,10 +23466,10 @@
         </is>
       </c>
       <c r="B1772" s="2" t="n">
-        <v>46082</v>
+        <v>46023</v>
       </c>
       <c r="C1772" t="n">
-        <v>101997</v>
+        <v>75362</v>
       </c>
     </row>
     <row r="1773">
@@ -23479,10 +23479,10 @@
         </is>
       </c>
       <c r="B1773" s="2" t="n">
-        <v>46113</v>
+        <v>46054</v>
       </c>
       <c r="C1773" t="n">
-        <v>104298</v>
+        <v>88039</v>
       </c>
     </row>
     <row r="1774">
@@ -23492,10 +23492,10 @@
         </is>
       </c>
       <c r="B1774" s="2" t="n">
-        <v>46143</v>
+        <v>46082</v>
       </c>
       <c r="C1774" t="n">
-        <v>83442</v>
+        <v>101997</v>
       </c>
     </row>
     <row r="1775">
@@ -23505,10 +23505,10 @@
         </is>
       </c>
       <c r="B1775" s="2" t="n">
-        <v>46174</v>
+        <v>46113</v>
       </c>
       <c r="C1775" t="n">
-        <v>105041</v>
+        <v>104298</v>
       </c>
     </row>
     <row r="1776">
@@ -23518,10 +23518,10 @@
         </is>
       </c>
       <c r="B1776" s="2" t="n">
-        <v>46204</v>
+        <v>46143</v>
       </c>
       <c r="C1776" t="n">
-        <v>80786</v>
+        <v>83442</v>
       </c>
     </row>
     <row r="1777">
@@ -23531,36 +23531,36 @@
         </is>
       </c>
       <c r="B1777" s="2" t="n">
-        <v>46235</v>
+        <v>46174</v>
       </c>
       <c r="C1777" t="n">
-        <v>81031</v>
+        <v>105041</v>
       </c>
     </row>
     <row r="1778">
       <c r="A1778" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="B1778" s="2" t="n">
-        <v>42401</v>
+        <v>46204</v>
       </c>
       <c r="C1778" t="n">
-        <v>17.64</v>
+        <v>80786</v>
       </c>
     </row>
     <row r="1779">
       <c r="A1779" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="B1779" s="2" t="n">
-        <v>42430</v>
+        <v>46235</v>
       </c>
       <c r="C1779" t="n">
-        <v>16.826</v>
+        <v>81031</v>
       </c>
     </row>
     <row r="1780">
@@ -23570,10 +23570,10 @@
         </is>
       </c>
       <c r="B1780" s="2" t="n">
-        <v>42461</v>
+        <v>42401</v>
       </c>
       <c r="C1780" t="n">
-        <v>17.247</v>
+        <v>17.64</v>
       </c>
     </row>
     <row r="1781">
@@ -23583,10 +23583,10 @@
         </is>
       </c>
       <c r="B1781" s="2" t="n">
-        <v>42491</v>
+        <v>42430</v>
       </c>
       <c r="C1781" t="n">
-        <v>17.288</v>
+        <v>16.826</v>
       </c>
     </row>
     <row r="1782">
@@ -23596,10 +23596,10 @@
         </is>
       </c>
       <c r="B1782" s="2" t="n">
-        <v>42522</v>
+        <v>42461</v>
       </c>
       <c r="C1782" t="n">
-        <v>17.334</v>
+        <v>17.247</v>
       </c>
     </row>
     <row r="1783">
@@ -23609,10 +23609,10 @@
         </is>
       </c>
       <c r="B1783" s="2" t="n">
-        <v>42552</v>
+        <v>42491</v>
       </c>
       <c r="C1783" t="n">
-        <v>17.744</v>
+        <v>17.288</v>
       </c>
     </row>
     <row r="1784">
@@ -23622,10 +23622,10 @@
         </is>
       </c>
       <c r="B1784" s="2" t="n">
-        <v>42583</v>
+        <v>42522</v>
       </c>
       <c r="C1784" t="n">
-        <v>17.541</v>
+        <v>17.334</v>
       </c>
     </row>
     <row r="1785">
@@ -23635,10 +23635,10 @@
         </is>
       </c>
       <c r="B1785" s="2" t="n">
-        <v>42614</v>
+        <v>42552</v>
       </c>
       <c r="C1785" t="n">
-        <v>17.574</v>
+        <v>17.744</v>
       </c>
     </row>
     <row r="1786">
@@ -23648,10 +23648,10 @@
         </is>
       </c>
       <c r="B1786" s="2" t="n">
-        <v>42644</v>
+        <v>42583</v>
       </c>
       <c r="C1786" t="n">
-        <v>17.606</v>
+        <v>17.541</v>
       </c>
     </row>
     <row r="1787">
@@ -23661,10 +23661,10 @@
         </is>
       </c>
       <c r="B1787" s="2" t="n">
-        <v>42675</v>
+        <v>42614</v>
       </c>
       <c r="C1787" t="n">
-        <v>17.411</v>
+        <v>17.574</v>
       </c>
     </row>
     <row r="1788">
@@ -23674,10 +23674,10 @@
         </is>
       </c>
       <c r="B1788" s="2" t="n">
-        <v>42705</v>
+        <v>42644</v>
       </c>
       <c r="C1788" t="n">
-        <v>17.906</v>
+        <v>17.606</v>
       </c>
     </row>
     <row r="1789">
@@ -23687,10 +23687,10 @@
         </is>
       </c>
       <c r="B1789" s="2" t="n">
-        <v>42736</v>
+        <v>42675</v>
       </c>
       <c r="C1789" t="n">
-        <v>17.29</v>
+        <v>17.411</v>
       </c>
     </row>
     <row r="1790">
@@ -23700,10 +23700,10 @@
         </is>
       </c>
       <c r="B1790" s="2" t="n">
-        <v>42767</v>
+        <v>42705</v>
       </c>
       <c r="C1790" t="n">
-        <v>17.314</v>
+        <v>17.906</v>
       </c>
     </row>
     <row r="1791">
@@ -23713,10 +23713,10 @@
         </is>
       </c>
       <c r="B1791" s="2" t="n">
-        <v>42795</v>
+        <v>42736</v>
       </c>
       <c r="C1791" t="n">
-        <v>16.656</v>
+        <v>17.29</v>
       </c>
     </row>
     <row r="1792">
@@ -23726,10 +23726,10 @@
         </is>
       </c>
       <c r="B1792" s="2" t="n">
-        <v>42826</v>
+        <v>42767</v>
       </c>
       <c r="C1792" t="n">
-        <v>16.771</v>
+        <v>17.314</v>
       </c>
     </row>
     <row r="1793">
@@ -23739,10 +23739,10 @@
         </is>
       </c>
       <c r="B1793" s="2" t="n">
-        <v>42856</v>
+        <v>42795</v>
       </c>
       <c r="C1793" t="n">
-        <v>16.664</v>
+        <v>16.656</v>
       </c>
     </row>
     <row r="1794">
@@ -23752,10 +23752,10 @@
         </is>
       </c>
       <c r="B1794" s="2" t="n">
-        <v>42887</v>
+        <v>42826</v>
       </c>
       <c r="C1794" t="n">
-        <v>16.703</v>
+        <v>16.771</v>
       </c>
     </row>
     <row r="1795">
@@ -23765,10 +23765,10 @@
         </is>
       </c>
       <c r="B1795" s="2" t="n">
-        <v>42917</v>
+        <v>42856</v>
       </c>
       <c r="C1795" t="n">
-        <v>16.842</v>
+        <v>16.664</v>
       </c>
     </row>
     <row r="1796">
@@ -23778,10 +23778,10 @@
         </is>
       </c>
       <c r="B1796" s="2" t="n">
-        <v>42948</v>
+        <v>42887</v>
       </c>
       <c r="C1796" t="n">
-        <v>16.614</v>
+        <v>16.703</v>
       </c>
     </row>
     <row r="1797">
@@ -23791,10 +23791,10 @@
         </is>
       </c>
       <c r="B1797" s="2" t="n">
-        <v>42979</v>
+        <v>42917</v>
       </c>
       <c r="C1797" t="n">
-        <v>17.893</v>
+        <v>16.842</v>
       </c>
     </row>
     <row r="1798">
@@ -23804,10 +23804,10 @@
         </is>
       </c>
       <c r="B1798" s="2" t="n">
-        <v>43009</v>
+        <v>42948</v>
       </c>
       <c r="C1798" t="n">
-        <v>18.059</v>
+        <v>16.614</v>
       </c>
     </row>
     <row r="1799">
@@ -23817,10 +23817,10 @@
         </is>
       </c>
       <c r="B1799" s="2" t="n">
-        <v>43040</v>
+        <v>42979</v>
       </c>
       <c r="C1799" t="n">
-        <v>17.55</v>
+        <v>17.893</v>
       </c>
     </row>
     <row r="1800">
@@ -23830,10 +23830,10 @@
         </is>
       </c>
       <c r="B1800" s="2" t="n">
-        <v>43070</v>
+        <v>43009</v>
       </c>
       <c r="C1800" t="n">
-        <v>17.445</v>
+        <v>18.059</v>
       </c>
     </row>
     <row r="1801">
@@ -23843,10 +23843,10 @@
         </is>
       </c>
       <c r="B1801" s="2" t="n">
-        <v>43101</v>
+        <v>43040</v>
       </c>
       <c r="C1801" t="n">
-        <v>16.745</v>
+        <v>17.55</v>
       </c>
     </row>
     <row r="1802">
@@ -23856,10 +23856,10 @@
         </is>
       </c>
       <c r="B1802" s="2" t="n">
-        <v>43132</v>
+        <v>43070</v>
       </c>
       <c r="C1802" t="n">
-        <v>16.974</v>
+        <v>17.445</v>
       </c>
     </row>
     <row r="1803">
@@ -23869,10 +23869,10 @@
         </is>
       </c>
       <c r="B1803" s="2" t="n">
-        <v>43160</v>
+        <v>43101</v>
       </c>
       <c r="C1803" t="n">
-        <v>17.196</v>
+        <v>16.745</v>
       </c>
     </row>
     <row r="1804">
@@ -23882,10 +23882,10 @@
         </is>
       </c>
       <c r="B1804" s="2" t="n">
-        <v>43191</v>
+        <v>43132</v>
       </c>
       <c r="C1804" t="n">
-        <v>17.117</v>
+        <v>16.974</v>
       </c>
     </row>
     <row r="1805">
@@ -23895,10 +23895,10 @@
         </is>
       </c>
       <c r="B1805" s="2" t="n">
-        <v>43221</v>
+        <v>43160</v>
       </c>
       <c r="C1805" t="n">
-        <v>17.342</v>
+        <v>17.196</v>
       </c>
     </row>
     <row r="1806">
@@ -23908,10 +23908,10 @@
         </is>
       </c>
       <c r="B1806" s="2" t="n">
-        <v>43252</v>
+        <v>43191</v>
       </c>
       <c r="C1806" t="n">
-        <v>17.25</v>
+        <v>17.117</v>
       </c>
     </row>
     <row r="1807">
@@ -23921,10 +23921,10 @@
         </is>
       </c>
       <c r="B1807" s="2" t="n">
-        <v>43282</v>
+        <v>43221</v>
       </c>
       <c r="C1807" t="n">
-        <v>17.137</v>
+        <v>17.342</v>
       </c>
     </row>
     <row r="1808">
@@ -23934,10 +23934,10 @@
         </is>
       </c>
       <c r="B1808" s="2" t="n">
-        <v>43313</v>
+        <v>43252</v>
       </c>
       <c r="C1808" t="n">
-        <v>17.044</v>
+        <v>17.25</v>
       </c>
     </row>
     <row r="1809">
@@ -23947,10 +23947,10 @@
         </is>
       </c>
       <c r="B1809" s="2" t="n">
-        <v>43344</v>
+        <v>43282</v>
       </c>
       <c r="C1809" t="n">
-        <v>17.28</v>
+        <v>17.137</v>
       </c>
     </row>
     <row r="1810">
@@ -23960,10 +23960,10 @@
         </is>
       </c>
       <c r="B1810" s="2" t="n">
-        <v>43374</v>
+        <v>43313</v>
       </c>
       <c r="C1810" t="n">
-        <v>17.469</v>
+        <v>17.044</v>
       </c>
     </row>
     <row r="1811">
@@ -23973,10 +23973,10 @@
         </is>
       </c>
       <c r="B1811" s="2" t="n">
-        <v>43405</v>
+        <v>43344</v>
       </c>
       <c r="C1811" t="n">
-        <v>17.552</v>
+        <v>17.28</v>
       </c>
     </row>
     <row r="1812">
@@ -23986,10 +23986,10 @@
         </is>
       </c>
       <c r="B1812" s="2" t="n">
-        <v>43435</v>
+        <v>43374</v>
       </c>
       <c r="C1812" t="n">
-        <v>17.593</v>
+        <v>17.469</v>
       </c>
     </row>
     <row r="1813">
@@ -23999,10 +23999,10 @@
         </is>
       </c>
       <c r="B1813" s="2" t="n">
-        <v>43466</v>
+        <v>43405</v>
       </c>
       <c r="C1813" t="n">
-        <v>16.436</v>
+        <v>17.552</v>
       </c>
     </row>
     <row r="1814">
@@ -24012,10 +24012,10 @@
         </is>
       </c>
       <c r="B1814" s="2" t="n">
-        <v>43497</v>
+        <v>43435</v>
       </c>
       <c r="C1814" t="n">
-        <v>16.452</v>
+        <v>17.593</v>
       </c>
     </row>
     <row r="1815">
@@ -24025,10 +24025,10 @@
         </is>
       </c>
       <c r="B1815" s="2" t="n">
-        <v>43525</v>
+        <v>43466</v>
       </c>
       <c r="C1815" t="n">
-        <v>17.338</v>
+        <v>16.436</v>
       </c>
     </row>
     <row r="1816">
@@ -24038,10 +24038,10 @@
         </is>
       </c>
       <c r="B1816" s="2" t="n">
-        <v>43556</v>
+        <v>43497</v>
       </c>
       <c r="C1816" t="n">
-        <v>16.391</v>
+        <v>16.452</v>
       </c>
     </row>
     <row r="1817">
@@ -24051,10 +24051,10 @@
         </is>
       </c>
       <c r="B1817" s="2" t="n">
-        <v>43586</v>
+        <v>43525</v>
       </c>
       <c r="C1817" t="n">
-        <v>17.398</v>
+        <v>17.338</v>
       </c>
     </row>
     <row r="1818">
@@ -24064,10 +24064,10 @@
         </is>
       </c>
       <c r="B1818" s="2" t="n">
-        <v>43617</v>
+        <v>43556</v>
       </c>
       <c r="C1818" t="n">
-        <v>17.257</v>
+        <v>16.391</v>
       </c>
     </row>
     <row r="1819">
@@ -24077,10 +24077,10 @@
         </is>
       </c>
       <c r="B1819" s="2" t="n">
-        <v>43647</v>
+        <v>43586</v>
       </c>
       <c r="C1819" t="n">
-        <v>17.099</v>
+        <v>17.398</v>
       </c>
     </row>
     <row r="1820">
@@ -24090,10 +24090,10 @@
         </is>
       </c>
       <c r="B1820" s="2" t="n">
-        <v>43678</v>
+        <v>43617</v>
       </c>
       <c r="C1820" t="n">
-        <v>17.346</v>
+        <v>17.257</v>
       </c>
     </row>
     <row r="1821">
@@ -24103,10 +24103,10 @@
         </is>
       </c>
       <c r="B1821" s="2" t="n">
-        <v>43709</v>
+        <v>43647</v>
       </c>
       <c r="C1821" t="n">
-        <v>17.161</v>
+        <v>17.099</v>
       </c>
     </row>
     <row r="1822">
@@ -24116,10 +24116,10 @@
         </is>
       </c>
       <c r="B1822" s="2" t="n">
-        <v>43739</v>
+        <v>43678</v>
       </c>
       <c r="C1822" t="n">
-        <v>16.53</v>
+        <v>17.346</v>
       </c>
     </row>
     <row r="1823">
@@ -24129,10 +24129,10 @@
         </is>
       </c>
       <c r="B1823" s="2" t="n">
-        <v>43770</v>
+        <v>43709</v>
       </c>
       <c r="C1823" t="n">
-        <v>17.097</v>
+        <v>17.161</v>
       </c>
     </row>
     <row r="1824">
@@ -24142,10 +24142,10 @@
         </is>
       </c>
       <c r="B1824" s="2" t="n">
-        <v>43800</v>
+        <v>43739</v>
       </c>
       <c r="C1824" t="n">
-        <v>17.027</v>
+        <v>16.53</v>
       </c>
     </row>
     <row r="1825">
@@ -24155,10 +24155,10 @@
         </is>
       </c>
       <c r="B1825" s="2" t="n">
-        <v>43831</v>
+        <v>43770</v>
       </c>
       <c r="C1825" t="n">
-        <v>16.42</v>
+        <v>17.097</v>
       </c>
     </row>
     <row r="1826">
@@ -24168,10 +24168,10 @@
         </is>
       </c>
       <c r="B1826" s="2" t="n">
-        <v>43862</v>
+        <v>43800</v>
       </c>
       <c r="C1826" t="n">
-        <v>16.669</v>
+        <v>17.027</v>
       </c>
     </row>
     <row r="1827">
@@ -24181,10 +24181,10 @@
         </is>
       </c>
       <c r="B1827" s="2" t="n">
-        <v>43891</v>
+        <v>43831</v>
       </c>
       <c r="C1827" t="n">
-        <v>11.444</v>
+        <v>16.42</v>
       </c>
     </row>
     <row r="1828">
@@ -24194,10 +24194,10 @@
         </is>
       </c>
       <c r="B1828" s="2" t="n">
-        <v>43922</v>
+        <v>43862</v>
       </c>
       <c r="C1828" t="n">
-        <v>8.571</v>
+        <v>16.669</v>
       </c>
     </row>
     <row r="1829">
@@ -24207,10 +24207,10 @@
         </is>
       </c>
       <c r="B1829" s="2" t="n">
-        <v>43952</v>
+        <v>43891</v>
       </c>
       <c r="C1829" t="n">
-        <v>12.244</v>
+        <v>11.444</v>
       </c>
     </row>
     <row r="1830">
@@ -24220,10 +24220,10 @@
         </is>
       </c>
       <c r="B1830" s="2" t="n">
-        <v>43983</v>
+        <v>43922</v>
       </c>
       <c r="C1830" t="n">
-        <v>13.182</v>
+        <v>8.571</v>
       </c>
     </row>
     <row r="1831">
@@ -24233,10 +24233,10 @@
         </is>
       </c>
       <c r="B1831" s="2" t="n">
-        <v>44013</v>
+        <v>43952</v>
       </c>
       <c r="C1831" t="n">
-        <v>14.802</v>
+        <v>12.244</v>
       </c>
     </row>
     <row r="1832">
@@ -24246,10 +24246,10 @@
         </is>
       </c>
       <c r="B1832" s="2" t="n">
-        <v>44044</v>
+        <v>43983</v>
       </c>
       <c r="C1832" t="n">
-        <v>15.656</v>
+        <v>13.182</v>
       </c>
     </row>
     <row r="1833">
@@ -24259,10 +24259,10 @@
         </is>
       </c>
       <c r="B1833" s="2" t="n">
-        <v>44075</v>
+        <v>44013</v>
       </c>
       <c r="C1833" t="n">
-        <v>16.275</v>
+        <v>14.802</v>
       </c>
     </row>
     <row r="1834">
@@ -24272,10 +24272,10 @@
         </is>
       </c>
       <c r="B1834" s="2" t="n">
-        <v>44105</v>
+        <v>44044</v>
       </c>
       <c r="C1834" t="n">
-        <v>16.112</v>
+        <v>15.656</v>
       </c>
     </row>
     <row r="1835">
@@ -24285,10 +24285,10 @@
         </is>
       </c>
       <c r="B1835" s="2" t="n">
-        <v>44136</v>
+        <v>44075</v>
       </c>
       <c r="C1835" t="n">
-        <v>15.83</v>
+        <v>16.275</v>
       </c>
     </row>
     <row r="1836">
@@ -24298,10 +24298,10 @@
         </is>
       </c>
       <c r="B1836" s="2" t="n">
-        <v>44166</v>
+        <v>44105</v>
       </c>
       <c r="C1836" t="n">
-        <v>16.459</v>
+        <v>16.112</v>
       </c>
     </row>
     <row r="1837">
@@ -24311,10 +24311,10 @@
         </is>
       </c>
       <c r="B1837" s="2" t="n">
-        <v>44197</v>
+        <v>44136</v>
       </c>
       <c r="C1837" t="n">
-        <v>16.212</v>
+        <v>15.83</v>
       </c>
     </row>
     <row r="1838">
@@ -24324,10 +24324,10 @@
         </is>
       </c>
       <c r="B1838" s="2" t="n">
-        <v>44228</v>
+        <v>44166</v>
       </c>
       <c r="C1838" t="n">
-        <v>15.681</v>
+        <v>16.459</v>
       </c>
     </row>
     <row r="1839">
@@ -24337,10 +24337,10 @@
         </is>
       </c>
       <c r="B1839" s="2" t="n">
-        <v>44256</v>
+        <v>44197</v>
       </c>
       <c r="C1839" t="n">
-        <v>17.948</v>
+        <v>16.212</v>
       </c>
     </row>
     <row r="1840">
@@ -24350,10 +24350,10 @@
         </is>
       </c>
       <c r="B1840" s="2" t="n">
-        <v>44287</v>
+        <v>44228</v>
       </c>
       <c r="C1840" t="n">
-        <v>18.091</v>
+        <v>15.681</v>
       </c>
     </row>
     <row r="1841">
@@ -24363,10 +24363,10 @@
         </is>
       </c>
       <c r="B1841" s="2" t="n">
-        <v>44317</v>
+        <v>44256</v>
       </c>
       <c r="C1841" t="n">
-        <v>17.035</v>
+        <v>17.948</v>
       </c>
     </row>
     <row r="1842">
@@ -24376,10 +24376,10 @@
         </is>
       </c>
       <c r="B1842" s="2" t="n">
-        <v>44348</v>
+        <v>44287</v>
       </c>
       <c r="C1842" t="n">
-        <v>15.583</v>
+        <v>18.091</v>
       </c>
     </row>
     <row r="1843">
@@ -24389,10 +24389,10 @@
         </is>
       </c>
       <c r="B1843" s="2" t="n">
-        <v>44378</v>
+        <v>44317</v>
       </c>
       <c r="C1843" t="n">
-        <v>14.745</v>
+        <v>17.035</v>
       </c>
     </row>
     <row r="1844">
@@ -24402,10 +24402,10 @@
         </is>
       </c>
       <c r="B1844" s="2" t="n">
-        <v>44409</v>
+        <v>44348</v>
       </c>
       <c r="C1844" t="n">
-        <v>13.454</v>
+        <v>15.583</v>
       </c>
     </row>
     <row r="1845">
@@ -24415,10 +24415,10 @@
         </is>
       </c>
       <c r="B1845" s="2" t="n">
-        <v>44440</v>
+        <v>44378</v>
       </c>
       <c r="C1845" t="n">
-        <v>12.308</v>
+        <v>14.745</v>
       </c>
     </row>
     <row r="1846">
@@ -24428,10 +24428,10 @@
         </is>
       </c>
       <c r="B1846" s="2" t="n">
-        <v>44470</v>
+        <v>44409</v>
       </c>
       <c r="C1846" t="n">
-        <v>12.712</v>
+        <v>13.454</v>
       </c>
     </row>
     <row r="1847">
@@ -24441,10 +24441,10 @@
         </is>
       </c>
       <c r="B1847" s="2" t="n">
-        <v>44501</v>
+        <v>44440</v>
       </c>
       <c r="C1847" t="n">
-        <v>12.932</v>
+        <v>12.308</v>
       </c>
     </row>
     <row r="1848">
@@ -24454,10 +24454,10 @@
         </is>
       </c>
       <c r="B1848" s="2" t="n">
-        <v>44531</v>
+        <v>44470</v>
       </c>
       <c r="C1848" t="n">
-        <v>12.662</v>
+        <v>12.712</v>
       </c>
     </row>
     <row r="1849">
@@ -24467,10 +24467,10 @@
         </is>
       </c>
       <c r="B1849" s="2" t="n">
-        <v>44562</v>
+        <v>44501</v>
       </c>
       <c r="C1849" t="n">
-        <v>14.447</v>
+        <v>12.932</v>
       </c>
     </row>
     <row r="1850">
@@ -24480,10 +24480,10 @@
         </is>
       </c>
       <c r="B1850" s="2" t="n">
-        <v>44593</v>
+        <v>44531</v>
       </c>
       <c r="C1850" t="n">
-        <v>13.741</v>
+        <v>12.662</v>
       </c>
     </row>
     <row r="1851">
@@ -24493,10 +24493,10 @@
         </is>
       </c>
       <c r="B1851" s="2" t="n">
-        <v>44621</v>
+        <v>44562</v>
       </c>
       <c r="C1851" t="n">
-        <v>13.765</v>
+        <v>14.447</v>
       </c>
     </row>
     <row r="1852">
@@ -24506,10 +24506,10 @@
         </is>
       </c>
       <c r="B1852" s="2" t="n">
-        <v>44652</v>
+        <v>44593</v>
       </c>
       <c r="C1852" t="n">
-        <v>14.161</v>
+        <v>13.741</v>
       </c>
     </row>
     <row r="1853">
@@ -24519,10 +24519,10 @@
         </is>
       </c>
       <c r="B1853" s="2" t="n">
-        <v>44682</v>
+        <v>44621</v>
       </c>
       <c r="C1853" t="n">
-        <v>12.833</v>
+        <v>13.765</v>
       </c>
     </row>
     <row r="1854">
@@ -24532,10 +24532,10 @@
         </is>
       </c>
       <c r="B1854" s="2" t="n">
-        <v>44713</v>
+        <v>44652</v>
       </c>
       <c r="C1854" t="n">
-        <v>13.35</v>
+        <v>14.161</v>
       </c>
     </row>
     <row r="1855">
@@ -24545,10 +24545,10 @@
         </is>
       </c>
       <c r="B1855" s="2" t="n">
-        <v>44743</v>
+        <v>44682</v>
       </c>
       <c r="C1855" t="n">
-        <v>13.388</v>
+        <v>12.833</v>
       </c>
     </row>
     <row r="1856">
@@ -24558,10 +24558,10 @@
         </is>
       </c>
       <c r="B1856" s="2" t="n">
-        <v>44774</v>
+        <v>44713</v>
       </c>
       <c r="C1856" t="n">
-        <v>13.695</v>
+        <v>13.35</v>
       </c>
     </row>
     <row r="1857">
@@ -24571,10 +24571,10 @@
         </is>
       </c>
       <c r="B1857" s="2" t="n">
-        <v>44805</v>
+        <v>44743</v>
       </c>
       <c r="C1857" t="n">
-        <v>13.639</v>
+        <v>13.388</v>
       </c>
     </row>
     <row r="1858">
@@ -24584,10 +24584,10 @@
         </is>
       </c>
       <c r="B1858" s="2" t="n">
-        <v>44835</v>
+        <v>44774</v>
       </c>
       <c r="C1858" t="n">
-        <v>14.594</v>
+        <v>13.695</v>
       </c>
     </row>
     <row r="1859">
@@ -24597,10 +24597,10 @@
         </is>
       </c>
       <c r="B1859" s="2" t="n">
-        <v>44866</v>
+        <v>44805</v>
       </c>
       <c r="C1859" t="n">
-        <v>14.073</v>
+        <v>13.639</v>
       </c>
     </row>
     <row r="1860">
@@ -24610,10 +24610,10 @@
         </is>
       </c>
       <c r="B1860" s="2" t="n">
-        <v>44896</v>
+        <v>44835</v>
       </c>
       <c r="C1860" t="n">
-        <v>13.366</v>
+        <v>14.594</v>
       </c>
     </row>
     <row r="1861">
@@ -24623,10 +24623,10 @@
         </is>
       </c>
       <c r="B1861" s="2" t="n">
-        <v>44927</v>
+        <v>44866</v>
       </c>
       <c r="C1861" t="n">
-        <v>15.153</v>
+        <v>14.073</v>
       </c>
     </row>
     <row r="1862">
@@ -24636,10 +24636,10 @@
         </is>
       </c>
       <c r="B1862" s="2" t="n">
-        <v>44958</v>
+        <v>44896</v>
       </c>
       <c r="C1862" t="n">
-        <v>14.949</v>
+        <v>13.366</v>
       </c>
     </row>
     <row r="1863">
@@ -24649,10 +24649,10 @@
         </is>
       </c>
       <c r="B1863" s="2" t="n">
-        <v>44986</v>
+        <v>44927</v>
       </c>
       <c r="C1863" t="n">
-        <v>15.128</v>
+        <v>15.153</v>
       </c>
     </row>
     <row r="1864">
@@ -24662,10 +24662,10 @@
         </is>
       </c>
       <c r="B1864" s="2" t="n">
-        <v>45017</v>
+        <v>44958</v>
       </c>
       <c r="C1864" t="n">
-        <v>15.858</v>
+        <v>14.949</v>
       </c>
     </row>
     <row r="1865">
@@ -24675,10 +24675,10 @@
         </is>
       </c>
       <c r="B1865" s="2" t="n">
-        <v>45047</v>
+        <v>44986</v>
       </c>
       <c r="C1865" t="n">
-        <v>15.39</v>
+        <v>15.128</v>
       </c>
     </row>
     <row r="1866">
@@ -24688,10 +24688,10 @@
         </is>
       </c>
       <c r="B1866" s="2" t="n">
-        <v>45078</v>
+        <v>45017</v>
       </c>
       <c r="C1866" t="n">
-        <v>16.071</v>
+        <v>15.858</v>
       </c>
     </row>
     <row r="1867">
@@ -24701,10 +24701,10 @@
         </is>
       </c>
       <c r="B1867" s="2" t="n">
-        <v>45108</v>
+        <v>45047</v>
       </c>
       <c r="C1867" t="n">
-        <v>15.811</v>
+        <v>15.39</v>
       </c>
     </row>
     <row r="1868">
@@ -24714,10 +24714,10 @@
         </is>
       </c>
       <c r="B1868" s="2" t="n">
-        <v>45139</v>
+        <v>45078</v>
       </c>
       <c r="C1868" t="n">
-        <v>15.557</v>
+        <v>16.071</v>
       </c>
     </row>
     <row r="1869">
@@ -24727,10 +24727,10 @@
         </is>
       </c>
       <c r="B1869" s="2" t="n">
-        <v>45170</v>
+        <v>45108</v>
       </c>
       <c r="C1869" t="n">
-        <v>15.702</v>
+        <v>15.811</v>
       </c>
     </row>
     <row r="1870">
@@ -24740,10 +24740,10 @@
         </is>
       </c>
       <c r="B1870" s="2" t="n">
-        <v>45200</v>
+        <v>45139</v>
       </c>
       <c r="C1870" t="n">
-        <v>15.27</v>
+        <v>15.557</v>
       </c>
     </row>
     <row r="1871">
@@ -24753,10 +24753,10 @@
         </is>
       </c>
       <c r="B1871" s="2" t="n">
-        <v>45231</v>
+        <v>45170</v>
       </c>
       <c r="C1871" t="n">
-        <v>15.307</v>
+        <v>15.702</v>
       </c>
     </row>
     <row r="1872">
@@ -24766,10 +24766,10 @@
         </is>
       </c>
       <c r="B1872" s="2" t="n">
-        <v>45261</v>
+        <v>45200</v>
       </c>
       <c r="C1872" t="n">
-        <v>15.834</v>
+        <v>15.27</v>
       </c>
     </row>
     <row r="1873">
@@ -24779,10 +24779,10 @@
         </is>
       </c>
       <c r="B1873" s="2" t="n">
-        <v>45292</v>
+        <v>45231</v>
       </c>
       <c r="C1873" t="n">
-        <v>15.065</v>
+        <v>15.307</v>
       </c>
     </row>
     <row r="1874">
@@ -24792,10 +24792,10 @@
         </is>
       </c>
       <c r="B1874" s="2" t="n">
-        <v>45323</v>
+        <v>45261</v>
       </c>
       <c r="C1874" t="n">
-        <v>15.759</v>
+        <v>15.834</v>
       </c>
     </row>
     <row r="1875">
@@ -24805,10 +24805,10 @@
         </is>
       </c>
       <c r="B1875" s="2" t="n">
-        <v>45352</v>
+        <v>45292</v>
       </c>
       <c r="C1875" t="n">
-        <v>15.728</v>
+        <v>15.065</v>
       </c>
     </row>
     <row r="1876">
@@ -24818,10 +24818,10 @@
         </is>
       </c>
       <c r="B1876" s="2" t="n">
-        <v>45383</v>
+        <v>45323</v>
       </c>
       <c r="C1876" t="n">
-        <v>15.978</v>
+        <v>15.759</v>
       </c>
     </row>
     <row r="1877">
@@ -24831,10 +24831,10 @@
         </is>
       </c>
       <c r="B1877" s="2" t="n">
-        <v>45413</v>
+        <v>45352</v>
       </c>
       <c r="C1877" t="n">
-        <v>15.888</v>
+        <v>15.728</v>
       </c>
     </row>
     <row r="1878">
@@ -24844,10 +24844,10 @@
         </is>
       </c>
       <c r="B1878" s="2" t="n">
-        <v>45444</v>
+        <v>45383</v>
       </c>
       <c r="C1878" t="n">
-        <v>15.323</v>
+        <v>15.978</v>
       </c>
     </row>
     <row r="1879">
@@ -24857,10 +24857,10 @@
         </is>
       </c>
       <c r="B1879" s="2" t="n">
-        <v>45474</v>
+        <v>45413</v>
       </c>
       <c r="C1879" t="n">
-        <v>15.842</v>
+        <v>15.888</v>
       </c>
     </row>
     <row r="1880">
@@ -24870,10 +24870,10 @@
         </is>
       </c>
       <c r="B1880" s="2" t="n">
-        <v>45505</v>
+        <v>45444</v>
       </c>
       <c r="C1880" t="n">
-        <v>15.484</v>
+        <v>15.323</v>
       </c>
     </row>
     <row r="1881">
@@ -24883,10 +24883,10 @@
         </is>
       </c>
       <c r="B1881" s="2" t="n">
-        <v>45536</v>
+        <v>45474</v>
       </c>
       <c r="C1881" t="n">
-        <v>15.86</v>
+        <v>15.842</v>
       </c>
     </row>
     <row r="1882">
@@ -24896,10 +24896,10 @@
         </is>
       </c>
       <c r="B1882" s="2" t="n">
-        <v>45566</v>
+        <v>45505</v>
       </c>
       <c r="C1882" t="n">
-        <v>16.029</v>
+        <v>15.484</v>
       </c>
     </row>
     <row r="1883">
@@ -24909,10 +24909,10 @@
         </is>
       </c>
       <c r="B1883" s="2" t="n">
-        <v>45597</v>
+        <v>45536</v>
       </c>
       <c r="C1883" t="n">
-        <v>16.417</v>
+        <v>15.86</v>
       </c>
     </row>
     <row r="1884">
@@ -24922,10 +24922,10 @@
         </is>
       </c>
       <c r="B1884" s="2" t="n">
-        <v>45627</v>
+        <v>45566</v>
       </c>
       <c r="C1884" t="n">
-        <v>16.84</v>
+        <v>16.029</v>
       </c>
     </row>
     <row r="1885">
@@ -24935,10 +24935,10 @@
         </is>
       </c>
       <c r="B1885" s="2" t="n">
-        <v>45658</v>
+        <v>45597</v>
       </c>
       <c r="C1885" t="n">
-        <v>15.476</v>
+        <v>16.417</v>
       </c>
     </row>
     <row r="1886">
@@ -24948,10 +24948,10 @@
         </is>
       </c>
       <c r="B1886" s="2" t="n">
-        <v>45689</v>
+        <v>45627</v>
       </c>
       <c r="C1886" t="n">
-        <v>15.974</v>
+        <v>16.84</v>
       </c>
     </row>
     <row r="1887">
@@ -24961,10 +24961,10 @@
         </is>
       </c>
       <c r="B1887" s="2" t="n">
-        <v>45717</v>
+        <v>45658</v>
       </c>
       <c r="C1887" t="n">
-        <v>17.892</v>
+        <v>15.476</v>
       </c>
     </row>
     <row r="1888">
@@ -24974,10 +24974,10 @@
         </is>
       </c>
       <c r="B1888" s="2" t="n">
-        <v>45748</v>
+        <v>45689</v>
       </c>
       <c r="C1888" t="n">
-        <v>17.132</v>
+        <v>15.974</v>
       </c>
     </row>
     <row r="1889">
@@ -24987,10 +24987,10 @@
         </is>
       </c>
       <c r="B1889" s="2" t="n">
-        <v>45778</v>
+        <v>45717</v>
       </c>
       <c r="C1889" t="n">
-        <v>15.589</v>
+        <v>17.892</v>
       </c>
     </row>
     <row r="1890">
@@ -25000,10 +25000,10 @@
         </is>
       </c>
       <c r="B1890" s="2" t="n">
-        <v>45809</v>
+        <v>45748</v>
       </c>
       <c r="C1890" t="n">
-        <v>15.829</v>
+        <v>17.132</v>
       </c>
     </row>
     <row r="1891">
@@ -25013,10 +25013,10 @@
         </is>
       </c>
       <c r="B1891" s="2" t="n">
-        <v>45839</v>
+        <v>45778</v>
       </c>
       <c r="C1891" t="n">
-        <v>16.576</v>
+        <v>15.589</v>
       </c>
     </row>
     <row r="1892">
@@ -25026,10 +25026,10 @@
         </is>
       </c>
       <c r="B1892" s="2" t="n">
-        <v>45870</v>
+        <v>45809</v>
       </c>
       <c r="C1892" t="n">
-        <v>16.5</v>
+        <v>15.829</v>
       </c>
     </row>
     <row r="1893">
@@ -25039,10 +25039,10 @@
         </is>
       </c>
       <c r="B1893" s="2" t="n">
-        <v>45901</v>
+        <v>45839</v>
       </c>
       <c r="C1893" t="n">
-        <v>16.601</v>
+        <v>16.576</v>
       </c>
     </row>
     <row r="1894">
@@ -25052,10 +25052,10 @@
         </is>
       </c>
       <c r="B1894" s="2" t="n">
-        <v>45931</v>
+        <v>45870</v>
       </c>
       <c r="C1894" t="n">
-        <v>15.505</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="1895">
@@ -25065,10 +25065,10 @@
         </is>
       </c>
       <c r="B1895" s="2" t="n">
-        <v>45962</v>
+        <v>45901</v>
       </c>
       <c r="C1895" t="n">
-        <v>15.669</v>
+        <v>16.601</v>
       </c>
     </row>
     <row r="1896">
@@ -25078,10 +25078,10 @@
         </is>
       </c>
       <c r="B1896" s="2" t="n">
-        <v>45992</v>
+        <v>45931</v>
       </c>
       <c r="C1896" t="n">
-        <v>16.008</v>
+        <v>15.505</v>
       </c>
     </row>
     <row r="1897">
@@ -25091,10 +25091,10 @@
         </is>
       </c>
       <c r="B1897" s="2" t="n">
-        <v>46023</v>
+        <v>45962</v>
       </c>
       <c r="C1897" t="n">
-        <v>14.61</v>
+        <v>15.669</v>
       </c>
     </row>
     <row r="1898">
@@ -25104,10 +25104,10 @@
         </is>
       </c>
       <c r="B1898" s="2" t="n">
-        <v>46054</v>
+        <v>45992</v>
       </c>
       <c r="C1898" t="n">
-        <v>15.517</v>
+        <v>16.008</v>
       </c>
     </row>
     <row r="1899">
@@ -25117,10 +25117,10 @@
         </is>
       </c>
       <c r="B1899" s="2" t="n">
-        <v>46082</v>
+        <v>46023</v>
       </c>
       <c r="C1899" t="n">
-        <v>16.293</v>
+        <v>14.61</v>
       </c>
     </row>
     <row r="1900">
@@ -25130,10 +25130,10 @@
         </is>
       </c>
       <c r="B1900" s="2" t="n">
-        <v>46113</v>
+        <v>46054</v>
       </c>
       <c r="C1900" t="n">
-        <v>16.26</v>
+        <v>15.517</v>
       </c>
     </row>
     <row r="1901">
@@ -25143,10 +25143,10 @@
         </is>
       </c>
       <c r="B1901" s="2" t="n">
-        <v>46143</v>
+        <v>46082</v>
       </c>
       <c r="C1901" t="n">
-        <v>16.323</v>
+        <v>16.293</v>
       </c>
     </row>
     <row r="1902">
@@ -25156,10 +25156,10 @@
         </is>
       </c>
       <c r="B1902" s="2" t="n">
-        <v>46174</v>
+        <v>46113</v>
       </c>
       <c r="C1902" t="n">
-        <v>16.56</v>
+        <v>16.26</v>
       </c>
     </row>
     <row r="1903">
@@ -25169,10 +25169,10 @@
         </is>
       </c>
       <c r="B1903" s="2" t="n">
-        <v>46204</v>
+        <v>46143</v>
       </c>
       <c r="C1903" t="n">
-        <v>16.3</v>
+        <v>16.323</v>
       </c>
     </row>
     <row r="1904">
@@ -25182,10 +25182,49 @@
         </is>
       </c>
       <c r="B1904" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C1904" t="n">
+        <v>16.56</v>
+      </c>
+    </row>
+    <row r="1905">
+      <c r="A1905" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B1905" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C1905" t="n">
+        <v>16.3</v>
+      </c>
+    </row>
+    <row r="1906">
+      <c r="A1906" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B1906" s="2" t="n">
         <v>46235</v>
       </c>
-      <c r="C1904" t="n">
+      <c r="C1906" t="n">
         <v>16.8</v>
+      </c>
+    </row>
+    <row r="1907">
+      <c r="A1907" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B1907" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="C1907" t="n">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
